--- a/TUCUMAN 1061/Junio/tucuman JUNIO.xlsx
+++ b/TUCUMAN 1061/Junio/tucuman JUNIO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\TUCUMAN 1061\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8591913C-CEBD-4399-BAE7-29DA9CD3350E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6D1AEAC-C1CF-4750-A288-A599BCE68F91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Calculo Servicios  (2)'!$A$6:$H$23</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Gastos!$A$1:$H$53</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Gastos!$A$1:$H$54</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">Planilla!$A$1:$R$39</definedName>
     <definedName name="CantOper" localSheetId="2">#REF!</definedName>
     <definedName name="CantOper">#REF!</definedName>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="168">
   <si>
     <t>Domicilio:</t>
   </si>
@@ -567,6 +567,9 @@
   </si>
   <si>
     <t>Administraciòn JUNIO 2025:</t>
+  </si>
+  <si>
+    <t>Sebastian</t>
   </si>
 </sst>
 </file>
@@ -589,7 +592,7 @@
     <numFmt numFmtId="175" formatCode="0.00000"/>
     <numFmt numFmtId="176" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
   </numFmts>
-  <fonts count="36" x14ac:knownFonts="1">
+  <fonts count="37" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -830,6 +833,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -1373,7 +1383,7 @@
     <xf numFmtId="170" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="1" fontId="26" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="246">
+  <cellXfs count="249">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1816,6 +1826,11 @@
     <xf numFmtId="1" fontId="27" fillId="8" borderId="29" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="166" fontId="36" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="23" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="36" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -2214,7 +2229,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N52"/>
+  <dimension ref="A1:N53"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
@@ -2370,7 +2385,7 @@
       <c r="E15" s="19"/>
       <c r="F15" s="19"/>
       <c r="G15" s="19"/>
-      <c r="H15" s="44">
+      <c r="H15" s="248">
         <v>4030.28</v>
       </c>
     </row>
@@ -2435,8 +2450,8 @@
       <c r="E20" s="19"/>
       <c r="F20" s="19"/>
       <c r="G20" s="19"/>
-      <c r="H20" s="26">
-        <v>400523.88</v>
+      <c r="H20" s="246">
+        <v>759222.49</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
@@ -2451,7 +2466,7 @@
       <c r="G21" s="22"/>
       <c r="H21" s="27">
         <f>SUM(H19:H20)</f>
-        <v>587490.78</v>
+        <v>946189.39</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
@@ -2490,15 +2505,15 @@
       <c r="E24" s="19"/>
       <c r="F24" s="19"/>
       <c r="G24" s="19"/>
-      <c r="H24" s="26">
+      <c r="H24" s="246">
         <v>42645</v>
       </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="100" t="s">
-        <v>163</v>
+      <c r="A25" s="247" t="s">
+        <v>167</v>
       </c>
       <c r="B25" s="19"/>
       <c r="C25" s="25"/>
@@ -2506,179 +2521,185 @@
       <c r="E25" s="19"/>
       <c r="F25" s="19"/>
       <c r="G25" s="19"/>
-      <c r="H25" s="26">
-        <v>380000</v>
+      <c r="H25" s="246">
+        <v>65000</v>
       </c>
       <c r="I25" s="14"/>
       <c r="J25" s="14"/>
     </row>
-    <row r="26" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="100" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
+      <c r="C26" s="25"/>
       <c r="D26" s="19"/>
       <c r="E26" s="19"/>
       <c r="F26" s="19"/>
       <c r="G26" s="19"/>
       <c r="H26" s="26">
+        <v>380000</v>
+      </c>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+    </row>
+    <row r="27" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="100" t="s">
+        <v>145</v>
+      </c>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="26">
         <v>65000</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="21" t="s">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B27" s="22"/>
-      <c r="C27" s="22"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="22"/>
-      <c r="H27" s="27">
-        <f>SUM(H23:H26)</f>
-        <v>1084443.52</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="212" t="s">
+      <c r="B28" s="22"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="27">
+        <f>SUM(H23:H27)</f>
+        <v>1149443.52</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="212" t="s">
         <v>62</v>
       </c>
-      <c r="B28" s="213"/>
-      <c r="C28" s="213"/>
-      <c r="D28" s="213"/>
-      <c r="E28" s="213"/>
-      <c r="F28" s="213"/>
-      <c r="G28" s="213"/>
-      <c r="H28" s="214"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="18" t="s">
+      <c r="B29" s="213"/>
+      <c r="C29" s="213"/>
+      <c r="D29" s="213"/>
+      <c r="E29" s="213"/>
+      <c r="F29" s="213"/>
+      <c r="G29" s="213"/>
+      <c r="H29" s="214"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19" t="s">
+      <c r="B30" s="19"/>
+      <c r="C30" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="46"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="21" t="s">
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="28"/>
+      <c r="I30" s="46"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="21" t="s">
         <v>166</v>
       </c>
-      <c r="B30" s="22"/>
-      <c r="C30" s="22"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="22"/>
-      <c r="G30" s="22"/>
-      <c r="H30" s="187">
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="187">
         <v>60592.67</v>
       </c>
-      <c r="I30" s="46"/>
-      <c r="N30" t="s">
+      <c r="I31" s="46"/>
+      <c r="N31" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="18"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="29"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="212" t="s">
+    <row r="32" spans="1:14" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="18"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="29"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="212" t="s">
         <v>63</v>
       </c>
-      <c r="B32" s="213"/>
-      <c r="C32" s="213"/>
-      <c r="D32" s="213"/>
-      <c r="E32" s="213"/>
-      <c r="F32" s="213"/>
-      <c r="G32" s="213"/>
-      <c r="H32" s="214"/>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="52"/>
-      <c r="B33" s="53"/>
-      <c r="C33" s="53"/>
-      <c r="D33" s="53"/>
-      <c r="E33" s="53"/>
-      <c r="F33" s="53"/>
-      <c r="G33" s="53"/>
-      <c r="H33" s="54"/>
-      <c r="J33" s="15"/>
-    </row>
-    <row r="34" spans="1:11" s="16" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="30" t="s">
+      <c r="B33" s="213"/>
+      <c r="C33" s="213"/>
+      <c r="D33" s="213"/>
+      <c r="E33" s="213"/>
+      <c r="F33" s="213"/>
+      <c r="G33" s="213"/>
+      <c r="H33" s="214"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="52"/>
+      <c r="B34" s="53"/>
+      <c r="C34" s="53"/>
+      <c r="D34" s="53"/>
+      <c r="E34" s="53"/>
+      <c r="F34" s="53"/>
+      <c r="G34" s="53"/>
+      <c r="H34" s="54"/>
+      <c r="J34" s="15"/>
+    </row>
+    <row r="35" spans="1:11" s="16" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="B34" s="31"/>
-      <c r="C34" s="31"/>
-      <c r="D34" s="31"/>
-      <c r="E34" s="31"/>
-      <c r="F34" s="31"/>
-      <c r="G34" s="31"/>
-      <c r="H34" s="32">
-        <f>H16+H21+H27+H30+H33</f>
-        <v>2110147.75</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" s="14" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="48" t="s">
+      <c r="B35" s="31"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="31"/>
+      <c r="E35" s="31"/>
+      <c r="F35" s="31"/>
+      <c r="G35" s="31"/>
+      <c r="H35" s="32">
+        <f>H16+H21+H28+H31+H34</f>
+        <v>2533846.36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" s="14" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="48" t="s">
         <v>152</v>
       </c>
-      <c r="B35" s="49"/>
-      <c r="C35" s="49"/>
-      <c r="D35" s="49"/>
-      <c r="E35" s="49"/>
-      <c r="F35" s="49"/>
-      <c r="G35" s="49"/>
-      <c r="H35" s="50"/>
-    </row>
-    <row r="36" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="202" t="s">
+      <c r="B36" s="49"/>
+      <c r="C36" s="49"/>
+      <c r="D36" s="49"/>
+      <c r="E36" s="49"/>
+      <c r="F36" s="49"/>
+      <c r="G36" s="49"/>
+      <c r="H36" s="50"/>
+    </row>
+    <row r="37" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="202" t="s">
         <v>12</v>
       </c>
-      <c r="B36" s="203"/>
-      <c r="C36" s="203"/>
-      <c r="D36" s="203"/>
-      <c r="E36" s="203"/>
-      <c r="F36" s="203"/>
-      <c r="G36" s="203"/>
-      <c r="H36" s="204"/>
-      <c r="I36" s="170"/>
-      <c r="K36" s="170"/>
-    </row>
-    <row r="37" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="205"/>
-      <c r="B37" s="206"/>
-      <c r="C37" s="206"/>
-      <c r="D37" s="206"/>
-      <c r="E37" s="206"/>
-      <c r="F37" s="206"/>
-      <c r="G37" s="206"/>
-      <c r="H37" s="207"/>
-    </row>
-    <row r="38" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="216"/>
-      <c r="B38" s="217"/>
-      <c r="C38" s="217"/>
-      <c r="D38" s="217"/>
-      <c r="E38" s="217"/>
-      <c r="F38" s="217"/>
-      <c r="G38" s="218"/>
-      <c r="H38" s="33"/>
+      <c r="B37" s="203"/>
+      <c r="C37" s="203"/>
+      <c r="D37" s="203"/>
+      <c r="E37" s="203"/>
+      <c r="F37" s="203"/>
+      <c r="G37" s="203"/>
+      <c r="H37" s="204"/>
+      <c r="I37" s="170"/>
+      <c r="K37" s="170"/>
+    </row>
+    <row r="38" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="205"/>
+      <c r="B38" s="206"/>
+      <c r="C38" s="206"/>
+      <c r="D38" s="206"/>
+      <c r="E38" s="206"/>
+      <c r="F38" s="206"/>
+      <c r="G38" s="206"/>
+      <c r="H38" s="207"/>
     </row>
     <row r="39" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="216"/>
@@ -2690,140 +2711,135 @@
       <c r="G39" s="218"/>
       <c r="H39" s="33"/>
     </row>
-    <row r="40" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="219"/>
-      <c r="B40" s="220"/>
-      <c r="C40" s="220"/>
-      <c r="D40" s="220"/>
-      <c r="E40" s="220"/>
-      <c r="F40" s="220"/>
-      <c r="G40" s="221"/>
+    <row r="40" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="216"/>
+      <c r="B40" s="217"/>
+      <c r="C40" s="217"/>
+      <c r="D40" s="217"/>
+      <c r="E40" s="217"/>
+      <c r="F40" s="217"/>
+      <c r="G40" s="218"/>
       <c r="H40" s="33"/>
     </row>
-    <row r="41" spans="1:11" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="222" t="s">
+    <row r="41" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="219"/>
+      <c r="B41" s="220"/>
+      <c r="C41" s="220"/>
+      <c r="D41" s="220"/>
+      <c r="E41" s="220"/>
+      <c r="F41" s="220"/>
+      <c r="G41" s="221"/>
+      <c r="H41" s="33"/>
+    </row>
+    <row r="42" spans="1:11" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="222" t="s">
         <v>16</v>
       </c>
-      <c r="B41" s="223"/>
-      <c r="C41" s="223"/>
-      <c r="D41" s="223"/>
-      <c r="E41" s="223"/>
-      <c r="F41" s="223"/>
-      <c r="G41" s="224"/>
-      <c r="H41" s="34">
-        <f>SUM(H38:H40)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" s="19"/>
-      <c r="B42" s="19"/>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="19"/>
-      <c r="G42" s="19"/>
-      <c r="H42" s="19"/>
-    </row>
-    <row r="43" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="223"/>
+      <c r="C42" s="223"/>
+      <c r="D42" s="223"/>
+      <c r="E42" s="223"/>
+      <c r="F42" s="223"/>
+      <c r="G42" s="224"/>
+      <c r="H42" s="34">
+        <f>SUM(H39:H41)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" s="19"/>
+      <c r="B43" s="19"/>
+      <c r="C43" s="19"/>
+      <c r="D43" s="19"/>
+      <c r="E43" s="19"/>
+      <c r="F43" s="19"/>
+      <c r="G43" s="19"/>
       <c r="H43" s="19"/>
-      <c r="J43" s="15"/>
-    </row>
-    <row r="44" spans="1:11" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="199" t="s">
+    </row>
+    <row r="44" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H44" s="19"/>
+      <c r="J44" s="15"/>
+    </row>
+    <row r="45" spans="1:11" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="199" t="s">
         <v>146</v>
       </c>
-      <c r="B44" s="199"/>
-      <c r="C44" s="199"/>
-      <c r="D44" s="199"/>
-      <c r="E44" s="199"/>
-      <c r="F44" s="199"/>
-      <c r="G44" s="199"/>
-      <c r="H44" s="32">
-        <f>+H34+H35</f>
-        <v>2110147.75</v>
-      </c>
-      <c r="J44" s="170"/>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" s="19"/>
-      <c r="B45" s="19"/>
-      <c r="C45" s="19"/>
-      <c r="D45" s="19"/>
-      <c r="E45" s="19"/>
-      <c r="F45" s="19"/>
-      <c r="G45" s="19"/>
-      <c r="H45" s="19"/>
-    </row>
-    <row r="46" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="30" t="s">
+      <c r="B45" s="199"/>
+      <c r="C45" s="199"/>
+      <c r="D45" s="199"/>
+      <c r="E45" s="199"/>
+      <c r="F45" s="199"/>
+      <c r="G45" s="199"/>
+      <c r="H45" s="32">
+        <f>+H35+H36</f>
+        <v>2533846.36</v>
+      </c>
+      <c r="J45" s="170"/>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46" s="19"/>
+      <c r="B46" s="19"/>
+      <c r="C46" s="19"/>
+      <c r="D46" s="19"/>
+      <c r="E46" s="19"/>
+      <c r="F46" s="19"/>
+      <c r="G46" s="19"/>
+      <c r="H46" s="19"/>
+    </row>
+    <row r="47" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A47" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="B46" s="31"/>
-      <c r="C46" s="31"/>
-      <c r="D46" s="31"/>
-      <c r="E46" s="31"/>
-      <c r="F46" s="31"/>
-      <c r="G46" s="31"/>
-      <c r="H46" s="35">
-        <f>H41</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A47" s="19"/>
-      <c r="B47" s="19"/>
-      <c r="C47" s="19"/>
-      <c r="D47" s="19"/>
-      <c r="E47" s="19"/>
-      <c r="F47" s="19"/>
-      <c r="G47" s="19"/>
-      <c r="H47" s="19"/>
-    </row>
-    <row r="48" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="208" t="s">
+      <c r="B47" s="31"/>
+      <c r="C47" s="31"/>
+      <c r="D47" s="31"/>
+      <c r="E47" s="31"/>
+      <c r="F47" s="31"/>
+      <c r="G47" s="31"/>
+      <c r="H47" s="35">
+        <f>H42</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48" s="19"/>
+      <c r="B48" s="19"/>
+      <c r="C48" s="19"/>
+      <c r="D48" s="19"/>
+      <c r="E48" s="19"/>
+      <c r="F48" s="19"/>
+      <c r="G48" s="19"/>
+      <c r="H48" s="19"/>
+    </row>
+    <row r="49" spans="1:10" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="208" t="s">
         <v>13</v>
       </c>
-      <c r="B48" s="209"/>
-      <c r="C48" s="209"/>
-      <c r="D48" s="209"/>
-      <c r="E48" s="209"/>
-      <c r="F48" s="209"/>
-      <c r="G48" s="209"/>
-      <c r="H48" s="210"/>
-    </row>
-    <row r="49" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="200" t="s">
+      <c r="B49" s="209"/>
+      <c r="C49" s="209"/>
+      <c r="D49" s="209"/>
+      <c r="E49" s="209"/>
+      <c r="F49" s="209"/>
+      <c r="G49" s="209"/>
+      <c r="H49" s="210"/>
+    </row>
+    <row r="50" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="200" t="s">
         <v>153</v>
       </c>
-      <c r="B49" s="200"/>
-      <c r="C49" s="200"/>
-      <c r="D49" s="200"/>
-      <c r="E49" s="200"/>
-      <c r="F49" s="200"/>
-      <c r="G49" s="200"/>
-      <c r="H49" s="41">
+      <c r="B50" s="200"/>
+      <c r="C50" s="200"/>
+      <c r="D50" s="200"/>
+      <c r="E50" s="200"/>
+      <c r="F50" s="200"/>
+      <c r="G50" s="200"/>
+      <c r="H50" s="41">
         <v>804075.47844455764</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" s="36" t="s">
-        <v>150</v>
-      </c>
-      <c r="B50" s="37"/>
-      <c r="C50" s="37"/>
-      <c r="D50" s="37"/>
-      <c r="E50" s="37"/>
-      <c r="F50" s="37"/>
-      <c r="G50" s="37"/>
-      <c r="H50" s="47">
-        <f>Planilla!I31</f>
-        <v>2414480.2154854122</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="36" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B51" s="37"/>
       <c r="C51" s="37"/>
@@ -2831,43 +2847,58 @@
       <c r="E51" s="37"/>
       <c r="F51" s="37"/>
       <c r="G51" s="37"/>
-      <c r="H51" s="38">
-        <f>-(H34+H41)</f>
-        <v>-2110147.75</v>
-      </c>
-      <c r="J51" s="15"/>
-    </row>
-    <row r="52" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A52" s="39" t="s">
+      <c r="H51" s="47">
+        <f>Planilla!I31</f>
+        <v>2414480.2154854122</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" s="36" t="s">
+        <v>151</v>
+      </c>
+      <c r="B52" s="37"/>
+      <c r="C52" s="37"/>
+      <c r="D52" s="37"/>
+      <c r="E52" s="37"/>
+      <c r="F52" s="37"/>
+      <c r="G52" s="37"/>
+      <c r="H52" s="38">
+        <f>-(H35+H42)</f>
+        <v>-2533846.36</v>
+      </c>
+      <c r="J52" s="15"/>
+    </row>
+    <row r="53" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A53" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="B52" s="40"/>
-      <c r="C52" s="40"/>
-      <c r="D52" s="40"/>
-      <c r="E52" s="40"/>
-      <c r="F52" s="40"/>
-      <c r="G52" s="40"/>
-      <c r="H52" s="51">
-        <f>SUM(H49:H51)</f>
-        <v>1108407.9439299698</v>
+      <c r="B53" s="40"/>
+      <c r="C53" s="40"/>
+      <c r="D53" s="40"/>
+      <c r="E53" s="40"/>
+      <c r="F53" s="40"/>
+      <c r="G53" s="40"/>
+      <c r="H53" s="51">
+        <f>SUM(H50:H52)</f>
+        <v>684709.33392996993</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A44:G44"/>
-    <mergeCell ref="A49:G49"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="A50:G50"/>
     <mergeCell ref="E3:F3"/>
-    <mergeCell ref="A36:H37"/>
-    <mergeCell ref="A48:H48"/>
+    <mergeCell ref="A37:H38"/>
+    <mergeCell ref="A49:H49"/>
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="A22:H22"/>
-    <mergeCell ref="A28:H28"/>
-    <mergeCell ref="A32:H32"/>
-    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A42:G42"/>
     <mergeCell ref="A40:G40"/>
-    <mergeCell ref="A41:G41"/>
-    <mergeCell ref="A39:G39"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>

--- a/TUCUMAN 1061/Junio/tucuman JUNIO.xlsx
+++ b/TUCUMAN 1061/Junio/tucuman JUNIO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\TUCUMAN 1061\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6D1AEAC-C1CF-4750-A288-A599BCE68F91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92B6A614-E4A3-48BA-90A0-37566623775C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Calculo Servicios  (2)'!$A$6:$H$23</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Gastos!$A$1:$H$54</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Gastos!$A$1:$H$53</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">Planilla!$A$1:$R$39</definedName>
     <definedName name="CantOper" localSheetId="2">#REF!</definedName>
     <definedName name="CantOper">#REF!</definedName>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="166">
   <si>
     <t>Domicilio:</t>
   </si>
@@ -383,9 +383,6 @@
     <t>Cecilia Mariel Cassettari</t>
   </si>
   <si>
-    <t>Grandinetti Leonardo Alberto</t>
-  </si>
-  <si>
     <t>Estevez Norberto Omar</t>
   </si>
   <si>
@@ -530,9 +527,6 @@
     <t>SALDO ANTERIOR</t>
   </si>
   <si>
-    <t>LAS LINEAS ROJAS SIGNIFICAN DEUDORES, ALGUNOS INCLUSO DE VARIOS MESES, A LA FECHA DE COBRO SE LE IMPUTARAN LOS PUNITORIOS, POR LO TANTO CADA UNO QUE DEBA ABONAR Y ADEUDE, ANTES DE IR DEBE CONSULTAR CUAL ES EL MONTO TOTAL QUE DEBE AFRONTAR CON EL TOTAL DE LA DEUDA Y LOS PUNITORIOS CORRESPONDIENTES. SALUDOS CORDIALES. LAS UNIDADES FUNCIONALES MARCAS SON LAS QUE PROVOCARAN EL CORTE DE LUZ. LA MISMA NO SE ABONARA MAS HASTA QUE TODOS PONGAN AL DIA LAS EXPENSAS.</t>
-  </si>
-  <si>
     <t>subidos en mar 2025</t>
   </si>
   <si>
@@ -545,9 +539,6 @@
     <t>TOTAL DE GASTOS EXTRAORDINARIOS</t>
   </si>
   <si>
-    <t>Kromacolor compra de materiales para terraza</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gasto Ordinario - Sin Edesur </t>
   </si>
   <si>
@@ -557,9 +548,6 @@
     <t>EDESUR:</t>
   </si>
   <si>
-    <t xml:space="preserve">Arreglo Lema ascensores - Reposicion y colocacion patin ascensor </t>
-  </si>
-  <si>
     <t xml:space="preserve">PERIODO: JUNIO </t>
   </si>
   <si>
@@ -569,7 +557,13 @@
     <t>Administraciòn JUNIO 2025:</t>
   </si>
   <si>
-    <t>Sebastian</t>
+    <t>SAC</t>
+  </si>
+  <si>
+    <t>Servicio de trabajo en impermeabilizacion de terraza - Sr. Lenoardo Balcazza</t>
+  </si>
+  <si>
+    <t>Perez Sebastian</t>
   </si>
 </sst>
 </file>
@@ -738,13 +732,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="16"/>
       <color theme="1"/>
@@ -840,6 +827,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -1378,12 +1371,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="1" fontId="24" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="1" fontId="25" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="1" fontId="26" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="249">
+  <cellXfs count="237">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1435,7 +1428,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="7" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="7" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1523,23 +1515,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="22" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="21" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="6" fillId="3" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="23" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="22" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="28" fillId="0" borderId="15" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="28" fillId="0" borderId="21" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="27" fillId="0" borderId="22" xfId="7" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="27" fillId="0" borderId="15" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="27" fillId="0" borderId="21" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="26" fillId="0" borderId="22" xfId="7" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="25" xfId="7" applyFont="1" applyBorder="1"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="3" xfId="7" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="18" fillId="0" borderId="3" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="6" applyFont="1"/>
-    <xf numFmtId="170" fontId="24" fillId="7" borderId="0" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="23" fillId="7" borderId="0" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="170" fontId="17" fillId="0" borderId="3" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1547,49 +1539,49 @@
     </xf>
     <xf numFmtId="167" fontId="17" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="17" fillId="3" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="26" fillId="0" borderId="0" xfId="8"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="25" fillId="0" borderId="0" xfId="8"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="22" xfId="7" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="26" fillId="0" borderId="23" xfId="8" applyBorder="1"/>
+    <xf numFmtId="1" fontId="25" fillId="0" borderId="23" xfId="8" applyBorder="1"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="23" xfId="7" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="26" fillId="0" borderId="24" xfId="8" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="24" xfId="8" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="37" xfId="7" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="26" fillId="0" borderId="18" xfId="8" applyBorder="1"/>
+    <xf numFmtId="1" fontId="25" fillId="0" borderId="18" xfId="8" applyBorder="1"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="18" xfId="7" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="26" fillId="0" borderId="38" xfId="8" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="26" fillId="0" borderId="3" xfId="8" applyBorder="1"/>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="38" xfId="8" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="25" fillId="0" borderId="3" xfId="8" applyBorder="1"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="3" xfId="7" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="26" fillId="0" borderId="32" xfId="8" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="26" fillId="0" borderId="0" xfId="8" applyNumberFormat="1"/>
-    <xf numFmtId="175" fontId="26" fillId="0" borderId="0" xfId="8" applyNumberFormat="1"/>
-    <xf numFmtId="172" fontId="26" fillId="0" borderId="0" xfId="8" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="27" fillId="0" borderId="25" xfId="8" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="27" fillId="0" borderId="3" xfId="8" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="27" fillId="0" borderId="32" xfId="8" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="26" fillId="0" borderId="0" xfId="8" quotePrefix="1"/>
-    <xf numFmtId="1" fontId="27" fillId="0" borderId="13" xfId="8" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="26" fillId="0" borderId="0" xfId="8" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="27" fillId="0" borderId="20" xfId="8" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="26" fillId="0" borderId="23" xfId="8" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="32" xfId="8" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="25" fillId="0" borderId="0" xfId="8" applyNumberFormat="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="8" applyNumberFormat="1"/>
+    <xf numFmtId="172" fontId="25" fillId="0" borderId="0" xfId="8" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="26" fillId="0" borderId="25" xfId="8" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="26" fillId="0" borderId="3" xfId="8" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="26" fillId="0" borderId="32" xfId="8" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="25" fillId="0" borderId="0" xfId="8" quotePrefix="1"/>
+    <xf numFmtId="1" fontId="26" fillId="0" borderId="13" xfId="8" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="25" fillId="0" borderId="0" xfId="8" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="26" fillId="0" borderId="20" xfId="8" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="25" fillId="0" borderId="23" xfId="8" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="18" fillId="0" borderId="23" xfId="8" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="27" fillId="0" borderId="23" xfId="8" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="29" fillId="0" borderId="24" xfId="8" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="26" fillId="0" borderId="23" xfId="8" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="28" fillId="0" borderId="24" xfId="8" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="18" fillId="0" borderId="3" xfId="8" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="30" fillId="0" borderId="26" xfId="8" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="26" fillId="0" borderId="0" xfId="8" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="30" fillId="0" borderId="27" xfId="8" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="29" fillId="0" borderId="26" xfId="8" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="173" fontId="25" fillId="0" borderId="0" xfId="8" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="29" fillId="0" borderId="27" xfId="8" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="18" fillId="0" borderId="28" xfId="8" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="18" fillId="0" borderId="19" xfId="8" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="26" fillId="7" borderId="0" xfId="8" applyFill="1"/>
+    <xf numFmtId="1" fontId="25" fillId="7" borderId="0" xfId="8" applyFill="1"/>
     <xf numFmtId="1" fontId="18" fillId="0" borderId="0" xfId="8" applyFont="1"/>
     <xf numFmtId="1" fontId="18" fillId="0" borderId="22" xfId="8" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="17" fillId="0" borderId="23" xfId="8" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1609,7 +1601,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="18" fillId="0" borderId="32" xfId="8" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1619,72 +1611,53 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="17" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="21" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="17" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
     <xf numFmtId="0" fontId="32" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="22" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="17" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
     <xf numFmtId="0" fontId="33" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="34" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="33" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
+    <xf numFmtId="2" fontId="32" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="20" fillId="9" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="18" fillId="9" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="17" fillId="9" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="17" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="22" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="8" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="22" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="21" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="18" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="8" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="17" fillId="5" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1763,22 +1736,19 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1799,23 +1769,14 @@
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="28" fillId="8" borderId="35" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="27" fillId="8" borderId="35" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="28" fillId="8" borderId="34" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="27" fillId="8" borderId="34" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="28" fillId="8" borderId="33" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="27" fillId="8" borderId="33" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="28" fillId="8" borderId="31" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="28" fillId="8" borderId="30" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="28" fillId="8" borderId="29" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="27" fillId="8" borderId="31" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1826,11 +1787,25 @@
     <xf numFmtId="1" fontId="27" fillId="8" borderId="29" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="36" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="23" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="36" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="26" fillId="8" borderId="31" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="26" fillId="8" borderId="30" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="26" fillId="8" borderId="29" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="29" fillId="5" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -2229,13 +2204,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N53"/>
+  <dimension ref="A1:N52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2254,7 +2228,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H2" s="6"/>
     </row>
@@ -2263,10 +2237,10 @@
       <c r="D3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="201">
+      <c r="E3" s="189">
         <v>1153202676</v>
       </c>
-      <c r="F3" s="201"/>
+      <c r="F3" s="189"/>
       <c r="H3" s="6"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2275,7 +2249,7 @@
         <v>2</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H4" s="6"/>
     </row>
@@ -2298,7 +2272,7 @@
       <c r="C7" s="10"/>
       <c r="D7" s="10"/>
       <c r="E7" s="10" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F7" s="10"/>
       <c r="G7" s="11"/>
@@ -2338,16 +2312,16 @@
       <c r="H11" s="8"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="211" t="s">
+      <c r="A12" s="199" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="211"/>
-      <c r="C12" s="211"/>
-      <c r="D12" s="211"/>
-      <c r="E12" s="211"/>
-      <c r="F12" s="211"/>
-      <c r="G12" s="211"/>
-      <c r="H12" s="211"/>
+      <c r="B12" s="199"/>
+      <c r="C12" s="199"/>
+      <c r="D12" s="199"/>
+      <c r="E12" s="199"/>
+      <c r="F12" s="199"/>
+      <c r="G12" s="199"/>
+      <c r="H12" s="199"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="18"/>
@@ -2364,7 +2338,7 @@
         <v>60</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C14" s="19"/>
       <c r="D14" s="19"/>
@@ -2376,8 +2350,8 @@
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="100" t="s">
-        <v>165</v>
+      <c r="A15" s="18" t="s">
+        <v>163</v>
       </c>
       <c r="B15" s="19"/>
       <c r="C15" s="19"/>
@@ -2385,64 +2359,65 @@
       <c r="E15" s="19"/>
       <c r="F15" s="19"/>
       <c r="G15" s="19"/>
-      <c r="H15" s="248">
+      <c r="H15" s="44">
+        <f>H14/2</f>
+        <v>186795.25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="99" t="s">
+        <v>161</v>
+      </c>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="44">
         <v>4030.28</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="21" t="s">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="22"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="195">
-        <f>SUM(H13:H15)</f>
-        <v>377620.78</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="23"/>
-      <c r="B17" s="24"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="24"/>
-      <c r="H17" s="43"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="212" t="s">
+      <c r="B17" s="22"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="184">
+        <f>SUM(H13:H16)</f>
+        <v>564416.03</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="23"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="43"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="200" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="213"/>
-      <c r="C18" s="213"/>
-      <c r="D18" s="213"/>
-      <c r="E18" s="213"/>
-      <c r="F18" s="213"/>
-      <c r="G18" s="213"/>
-      <c r="H18" s="214"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="B19" s="19"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="26">
-        <v>186966.9</v>
-      </c>
+      <c r="B19" s="201"/>
+      <c r="C19" s="201"/>
+      <c r="D19" s="201"/>
+      <c r="E19" s="201"/>
+      <c r="F19" s="201"/>
+      <c r="G19" s="201"/>
+      <c r="H19" s="202"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B20" s="19"/>
       <c r="C20" s="25"/>
@@ -2450,54 +2425,56 @@
       <c r="E20" s="19"/>
       <c r="F20" s="19"/>
       <c r="G20" s="19"/>
-      <c r="H20" s="246">
-        <v>759222.49</v>
+      <c r="H20" s="26">
+        <v>181578.15</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="21" t="s">
+      <c r="A21" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" s="19"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="26">
+        <f>759222.49-400523.88</f>
+        <v>358698.61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="22"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="27">
-        <f>SUM(H19:H20)</f>
-        <v>946189.39</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="215" t="s">
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="27">
+        <f>SUM(H20:H21)</f>
+        <v>540276.76</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="203" t="s">
         <v>61</v>
       </c>
-      <c r="B22" s="215"/>
-      <c r="C22" s="215"/>
-      <c r="D22" s="215"/>
-      <c r="E22" s="215"/>
-      <c r="F22" s="215"/>
-      <c r="G22" s="215"/>
-      <c r="H22" s="215"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="100" t="s">
-        <v>159</v>
-      </c>
-      <c r="B23" s="196"/>
-      <c r="C23" s="196"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="45">
-        <v>596798.52</v>
-      </c>
+      <c r="B23" s="203"/>
+      <c r="C23" s="203"/>
+      <c r="D23" s="203"/>
+      <c r="E23" s="203"/>
+      <c r="F23" s="203"/>
+      <c r="G23" s="203"/>
+      <c r="H23" s="203"/>
+      <c r="J23" s="26"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="100" t="s">
-        <v>143</v>
+      <c r="A24" s="99" t="s">
+        <v>142</v>
       </c>
       <c r="B24" s="19"/>
       <c r="C24" s="25"/>
@@ -2505,15 +2482,15 @@
       <c r="E24" s="19"/>
       <c r="F24" s="19"/>
       <c r="G24" s="19"/>
-      <c r="H24" s="246">
+      <c r="H24" s="26">
         <v>42645</v>
       </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="247" t="s">
-        <v>167</v>
+      <c r="A25" s="99" t="s">
+        <v>164</v>
       </c>
       <c r="B25" s="19"/>
       <c r="C25" s="25"/>
@@ -2521,320 +2498,319 @@
       <c r="E25" s="19"/>
       <c r="F25" s="19"/>
       <c r="G25" s="19"/>
-      <c r="H25" s="246">
-        <v>65000</v>
+      <c r="H25" s="26">
+        <v>550000</v>
       </c>
       <c r="I25" s="14"/>
       <c r="J25" s="14"/>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="100" t="s">
-        <v>163</v>
+    <row r="26" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="99" t="s">
+        <v>144</v>
       </c>
       <c r="B26" s="19"/>
-      <c r="C26" s="25"/>
+      <c r="C26" s="19"/>
       <c r="D26" s="19"/>
       <c r="E26" s="19"/>
       <c r="F26" s="19"/>
       <c r="G26" s="19"/>
       <c r="H26" s="26">
-        <v>380000</v>
-      </c>
-      <c r="I26" s="14"/>
-      <c r="J26" s="14"/>
-    </row>
-    <row r="27" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="100" t="s">
+        <v>65000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="22"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="27">
+        <f>SUM(H24:H26)</f>
+        <v>657645</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="200" t="s">
+        <v>62</v>
+      </c>
+      <c r="B28" s="201"/>
+      <c r="C28" s="201"/>
+      <c r="D28" s="201"/>
+      <c r="E28" s="201"/>
+      <c r="F28" s="201"/>
+      <c r="G28" s="201"/>
+      <c r="H28" s="202"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="45"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="B30" s="22"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+      <c r="H30" s="176">
+        <v>60592.67</v>
+      </c>
+      <c r="I30" s="45"/>
+      <c r="N30" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="18"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="29"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="200" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" s="201"/>
+      <c r="C32" s="201"/>
+      <c r="D32" s="201"/>
+      <c r="E32" s="201"/>
+      <c r="F32" s="201"/>
+      <c r="G32" s="201"/>
+      <c r="H32" s="202"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="51"/>
+      <c r="B33" s="52"/>
+      <c r="C33" s="52"/>
+      <c r="D33" s="52"/>
+      <c r="E33" s="52"/>
+      <c r="F33" s="52"/>
+      <c r="G33" s="52"/>
+      <c r="H33" s="53"/>
+      <c r="J33" s="15"/>
+    </row>
+    <row r="34" spans="1:11" s="16" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" s="31"/>
+      <c r="C34" s="31"/>
+      <c r="D34" s="31"/>
+      <c r="E34" s="31"/>
+      <c r="F34" s="31"/>
+      <c r="G34" s="31"/>
+      <c r="H34" s="32">
+        <f>H17+H22+H27+H30+H33</f>
+        <v>1822930.46</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" s="14" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="47" t="s">
+        <v>151</v>
+      </c>
+      <c r="B35" s="48"/>
+      <c r="C35" s="48"/>
+      <c r="D35" s="48"/>
+      <c r="E35" s="48"/>
+      <c r="F35" s="48"/>
+      <c r="G35" s="48"/>
+      <c r="H35" s="49"/>
+    </row>
+    <row r="36" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="190" t="s">
+        <v>12</v>
+      </c>
+      <c r="B36" s="191"/>
+      <c r="C36" s="191"/>
+      <c r="D36" s="191"/>
+      <c r="E36" s="191"/>
+      <c r="F36" s="191"/>
+      <c r="G36" s="191"/>
+      <c r="H36" s="192"/>
+      <c r="I36" s="169"/>
+      <c r="K36" s="169"/>
+    </row>
+    <row r="37" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="193"/>
+      <c r="B37" s="194"/>
+      <c r="C37" s="194"/>
+      <c r="D37" s="194"/>
+      <c r="E37" s="194"/>
+      <c r="F37" s="194"/>
+      <c r="G37" s="194"/>
+      <c r="H37" s="195"/>
+    </row>
+    <row r="38" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="204"/>
+      <c r="B38" s="205"/>
+      <c r="C38" s="205"/>
+      <c r="D38" s="205"/>
+      <c r="E38" s="205"/>
+      <c r="F38" s="205"/>
+      <c r="G38" s="206"/>
+      <c r="H38" s="33"/>
+    </row>
+    <row r="39" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="204"/>
+      <c r="B39" s="205"/>
+      <c r="C39" s="205"/>
+      <c r="D39" s="205"/>
+      <c r="E39" s="205"/>
+      <c r="F39" s="205"/>
+      <c r="G39" s="206"/>
+      <c r="H39" s="33"/>
+    </row>
+    <row r="40" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="207"/>
+      <c r="B40" s="208"/>
+      <c r="C40" s="208"/>
+      <c r="D40" s="208"/>
+      <c r="E40" s="208"/>
+      <c r="F40" s="208"/>
+      <c r="G40" s="209"/>
+      <c r="H40" s="33"/>
+    </row>
+    <row r="41" spans="1:11" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="210" t="s">
+        <v>16</v>
+      </c>
+      <c r="B41" s="211"/>
+      <c r="C41" s="211"/>
+      <c r="D41" s="211"/>
+      <c r="E41" s="211"/>
+      <c r="F41" s="211"/>
+      <c r="G41" s="212"/>
+      <c r="H41" s="34">
+        <f>SUM(H38:H40)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" s="19"/>
+      <c r="B42" s="19"/>
+      <c r="C42" s="19"/>
+      <c r="D42" s="19"/>
+      <c r="E42" s="19"/>
+      <c r="F42" s="19"/>
+      <c r="G42" s="19"/>
+      <c r="H42" s="19"/>
+    </row>
+    <row r="43" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H43" s="19"/>
+      <c r="J43" s="15"/>
+    </row>
+    <row r="44" spans="1:11" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="187" t="s">
         <v>145</v>
       </c>
-      <c r="B27" s="19"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="26">
-        <v>65000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="B28" s="22"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="22"/>
-      <c r="H28" s="27">
-        <f>SUM(H23:H27)</f>
-        <v>1149443.52</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="212" t="s">
-        <v>62</v>
-      </c>
-      <c r="B29" s="213"/>
-      <c r="C29" s="213"/>
-      <c r="D29" s="213"/>
-      <c r="E29" s="213"/>
-      <c r="F29" s="213"/>
-      <c r="G29" s="213"/>
-      <c r="H29" s="214"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="28"/>
-      <c r="I30" s="46"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="21" t="s">
-        <v>166</v>
-      </c>
-      <c r="B31" s="22"/>
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="22"/>
-      <c r="H31" s="187">
-        <v>60592.67</v>
-      </c>
-      <c r="I31" s="46"/>
-      <c r="N31" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="18"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="29"/>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="212" t="s">
-        <v>63</v>
-      </c>
-      <c r="B33" s="213"/>
-      <c r="C33" s="213"/>
-      <c r="D33" s="213"/>
-      <c r="E33" s="213"/>
-      <c r="F33" s="213"/>
-      <c r="G33" s="213"/>
-      <c r="H33" s="214"/>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="52"/>
-      <c r="B34" s="53"/>
-      <c r="C34" s="53"/>
-      <c r="D34" s="53"/>
-      <c r="E34" s="53"/>
-      <c r="F34" s="53"/>
-      <c r="G34" s="53"/>
-      <c r="H34" s="54"/>
-      <c r="J34" s="15"/>
-    </row>
-    <row r="35" spans="1:11" s="16" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35" s="31"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="31"/>
-      <c r="H35" s="32">
-        <f>H16+H21+H28+H31+H34</f>
-        <v>2533846.36</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" s="14" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="48" t="s">
+      <c r="B44" s="187"/>
+      <c r="C44" s="187"/>
+      <c r="D44" s="187"/>
+      <c r="E44" s="187"/>
+      <c r="F44" s="187"/>
+      <c r="G44" s="187"/>
+      <c r="H44" s="32">
+        <f>+H34+H35</f>
+        <v>1822930.46</v>
+      </c>
+      <c r="J44" s="169"/>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" s="19"/>
+      <c r="B45" s="19"/>
+      <c r="C45" s="19"/>
+      <c r="D45" s="19"/>
+      <c r="E45" s="19"/>
+      <c r="F45" s="19"/>
+      <c r="G45" s="19"/>
+      <c r="H45" s="19"/>
+    </row>
+    <row r="46" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A46" s="30" t="s">
+        <v>156</v>
+      </c>
+      <c r="B46" s="31"/>
+      <c r="C46" s="31"/>
+      <c r="D46" s="31"/>
+      <c r="E46" s="31"/>
+      <c r="F46" s="31"/>
+      <c r="G46" s="31"/>
+      <c r="H46" s="35">
+        <f>H41</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" s="19"/>
+      <c r="B47" s="19"/>
+      <c r="C47" s="19"/>
+      <c r="D47" s="19"/>
+      <c r="E47" s="19"/>
+      <c r="F47" s="19"/>
+      <c r="G47" s="19"/>
+      <c r="H47" s="19"/>
+    </row>
+    <row r="48" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="196" t="s">
+        <v>13</v>
+      </c>
+      <c r="B48" s="197"/>
+      <c r="C48" s="197"/>
+      <c r="D48" s="197"/>
+      <c r="E48" s="197"/>
+      <c r="F48" s="197"/>
+      <c r="G48" s="197"/>
+      <c r="H48" s="198"/>
+    </row>
+    <row r="49" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="188" t="s">
         <v>152</v>
       </c>
-      <c r="B36" s="49"/>
-      <c r="C36" s="49"/>
-      <c r="D36" s="49"/>
-      <c r="E36" s="49"/>
-      <c r="F36" s="49"/>
-      <c r="G36" s="49"/>
-      <c r="H36" s="50"/>
-    </row>
-    <row r="37" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="202" t="s">
-        <v>12</v>
-      </c>
-      <c r="B37" s="203"/>
-      <c r="C37" s="203"/>
-      <c r="D37" s="203"/>
-      <c r="E37" s="203"/>
-      <c r="F37" s="203"/>
-      <c r="G37" s="203"/>
-      <c r="H37" s="204"/>
-      <c r="I37" s="170"/>
-      <c r="K37" s="170"/>
-    </row>
-    <row r="38" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="205"/>
-      <c r="B38" s="206"/>
-      <c r="C38" s="206"/>
-      <c r="D38" s="206"/>
-      <c r="E38" s="206"/>
-      <c r="F38" s="206"/>
-      <c r="G38" s="206"/>
-      <c r="H38" s="207"/>
-    </row>
-    <row r="39" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="216"/>
-      <c r="B39" s="217"/>
-      <c r="C39" s="217"/>
-      <c r="D39" s="217"/>
-      <c r="E39" s="217"/>
-      <c r="F39" s="217"/>
-      <c r="G39" s="218"/>
-      <c r="H39" s="33"/>
-    </row>
-    <row r="40" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="216"/>
-      <c r="B40" s="217"/>
-      <c r="C40" s="217"/>
-      <c r="D40" s="217"/>
-      <c r="E40" s="217"/>
-      <c r="F40" s="217"/>
-      <c r="G40" s="218"/>
-      <c r="H40" s="33"/>
-    </row>
-    <row r="41" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="219"/>
-      <c r="B41" s="220"/>
-      <c r="C41" s="220"/>
-      <c r="D41" s="220"/>
-      <c r="E41" s="220"/>
-      <c r="F41" s="220"/>
-      <c r="G41" s="221"/>
-      <c r="H41" s="33"/>
-    </row>
-    <row r="42" spans="1:11" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="222" t="s">
-        <v>16</v>
-      </c>
-      <c r="B42" s="223"/>
-      <c r="C42" s="223"/>
-      <c r="D42" s="223"/>
-      <c r="E42" s="223"/>
-      <c r="F42" s="223"/>
-      <c r="G42" s="224"/>
-      <c r="H42" s="34">
-        <f>SUM(H39:H41)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A43" s="19"/>
-      <c r="B43" s="19"/>
-      <c r="C43" s="19"/>
-      <c r="D43" s="19"/>
-      <c r="E43" s="19"/>
-      <c r="F43" s="19"/>
-      <c r="G43" s="19"/>
-      <c r="H43" s="19"/>
-    </row>
-    <row r="44" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H44" s="19"/>
-      <c r="J44" s="15"/>
-    </row>
-    <row r="45" spans="1:11" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="199" t="s">
-        <v>146</v>
-      </c>
-      <c r="B45" s="199"/>
-      <c r="C45" s="199"/>
-      <c r="D45" s="199"/>
-      <c r="E45" s="199"/>
-      <c r="F45" s="199"/>
-      <c r="G45" s="199"/>
-      <c r="H45" s="32">
-        <f>+H35+H36</f>
-        <v>2533846.36</v>
-      </c>
-      <c r="J45" s="170"/>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A46" s="19"/>
-      <c r="B46" s="19"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="19"/>
-      <c r="E46" s="19"/>
-      <c r="F46" s="19"/>
-      <c r="G46" s="19"/>
-      <c r="H46" s="19"/>
-    </row>
-    <row r="47" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A47" s="30" t="s">
-        <v>158</v>
-      </c>
-      <c r="B47" s="31"/>
-      <c r="C47" s="31"/>
-      <c r="D47" s="31"/>
-      <c r="E47" s="31"/>
-      <c r="F47" s="31"/>
-      <c r="G47" s="31"/>
-      <c r="H47" s="35">
-        <f>H42</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A48" s="19"/>
-      <c r="B48" s="19"/>
-      <c r="C48" s="19"/>
-      <c r="D48" s="19"/>
-      <c r="E48" s="19"/>
-      <c r="F48" s="19"/>
-      <c r="G48" s="19"/>
-      <c r="H48" s="19"/>
-    </row>
-    <row r="49" spans="1:10" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="208" t="s">
-        <v>13</v>
-      </c>
-      <c r="B49" s="209"/>
-      <c r="C49" s="209"/>
-      <c r="D49" s="209"/>
-      <c r="E49" s="209"/>
-      <c r="F49" s="209"/>
-      <c r="G49" s="209"/>
-      <c r="H49" s="210"/>
-    </row>
-    <row r="50" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="200" t="s">
-        <v>153</v>
-      </c>
-      <c r="B50" s="200"/>
-      <c r="C50" s="200"/>
-      <c r="D50" s="200"/>
-      <c r="E50" s="200"/>
-      <c r="F50" s="200"/>
-      <c r="G50" s="200"/>
-      <c r="H50" s="41">
-        <v>804075.47844455764</v>
+      <c r="B49" s="188"/>
+      <c r="C49" s="188"/>
+      <c r="D49" s="188"/>
+      <c r="E49" s="188"/>
+      <c r="F49" s="188"/>
+      <c r="G49" s="188"/>
+      <c r="H49" s="41">
+        <v>1108407.9439299698</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" s="36" t="s">
+        <v>149</v>
+      </c>
+      <c r="B50" s="37"/>
+      <c r="C50" s="37"/>
+      <c r="D50" s="37"/>
+      <c r="E50" s="37"/>
+      <c r="F50" s="37"/>
+      <c r="G50" s="37"/>
+      <c r="H50" s="46">
+        <f>Planilla!I31</f>
+        <v>2672781.3927473403</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
@@ -2847,58 +2823,43 @@
       <c r="E51" s="37"/>
       <c r="F51" s="37"/>
       <c r="G51" s="37"/>
-      <c r="H51" s="47">
-        <f>Planilla!I31</f>
-        <v>2414480.2154854122</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A52" s="36" t="s">
-        <v>151</v>
-      </c>
-      <c r="B52" s="37"/>
-      <c r="C52" s="37"/>
-      <c r="D52" s="37"/>
-      <c r="E52" s="37"/>
-      <c r="F52" s="37"/>
-      <c r="G52" s="37"/>
-      <c r="H52" s="38">
-        <f>-(H35+H42)</f>
-        <v>-2533846.36</v>
-      </c>
-      <c r="J52" s="15"/>
-    </row>
-    <row r="53" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A53" s="39" t="s">
+      <c r="H51" s="38">
+        <f>-(H34+H41)</f>
+        <v>-1822930.46</v>
+      </c>
+      <c r="J51" s="15"/>
+    </row>
+    <row r="52" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A52" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="B53" s="40"/>
-      <c r="C53" s="40"/>
-      <c r="D53" s="40"/>
-      <c r="E53" s="40"/>
-      <c r="F53" s="40"/>
-      <c r="G53" s="40"/>
-      <c r="H53" s="51">
-        <f>SUM(H50:H52)</f>
-        <v>684709.33392996993</v>
+      <c r="B52" s="40"/>
+      <c r="C52" s="40"/>
+      <c r="D52" s="40"/>
+      <c r="E52" s="40"/>
+      <c r="F52" s="40"/>
+      <c r="G52" s="40"/>
+      <c r="H52" s="50">
+        <f>SUM(H49:H51)</f>
+        <v>1958258.8766773101</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="A50:G50"/>
+    <mergeCell ref="A44:G44"/>
+    <mergeCell ref="A49:G49"/>
     <mergeCell ref="E3:F3"/>
-    <mergeCell ref="A37:H38"/>
-    <mergeCell ref="A49:H49"/>
+    <mergeCell ref="A36:H37"/>
+    <mergeCell ref="A48:H48"/>
     <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="A29:H29"/>
-    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A41:G41"/>
     <mergeCell ref="A39:G39"/>
-    <mergeCell ref="A41:G41"/>
-    <mergeCell ref="A42:G42"/>
-    <mergeCell ref="A40:G40"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -2917,18 +2878,18 @@
   <dimension ref="A1:U38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.42578125" style="55" customWidth="1"/>
+    <col min="1" max="1" width="5.42578125" style="54" customWidth="1"/>
     <col min="2" max="2" width="11.28515625" hidden="1" customWidth="1"/>
     <col min="3" max="3" width="12.140625" customWidth="1"/>
     <col min="4" max="4" width="22.140625" customWidth="1"/>
     <col min="5" max="5" width="12.28515625" customWidth="1"/>
-    <col min="6" max="6" width="6.28515625" style="57" customWidth="1"/>
-    <col min="7" max="7" width="11.5703125" style="56" customWidth="1"/>
-    <col min="8" max="8" width="7.5703125" style="56" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="9.85546875" style="56" customWidth="1"/>
-    <col min="10" max="10" width="0.140625" style="56" customWidth="1"/>
-    <col min="11" max="11" width="11.140625" style="56" customWidth="1"/>
-    <col min="12" max="12" width="0.140625" style="56" customWidth="1"/>
+    <col min="6" max="6" width="6.28515625" style="56" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" style="55" customWidth="1"/>
+    <col min="8" max="8" width="7.5703125" style="55" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="9.85546875" style="55" customWidth="1"/>
+    <col min="10" max="10" width="0.140625" style="55" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" style="55" customWidth="1"/>
+    <col min="12" max="12" width="0.140625" style="55" customWidth="1"/>
     <col min="13" max="13" width="10.28515625" customWidth="1"/>
     <col min="14" max="14" width="12.85546875" customWidth="1"/>
     <col min="15" max="15" width="12.140625" customWidth="1"/>
@@ -2939,149 +2900,149 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="228" t="str">
+      <c r="A1" s="215" t="str">
         <f>Gastos!E7</f>
         <v xml:space="preserve">PERIODO: JUNIO </v>
       </c>
-      <c r="B1" s="229"/>
-      <c r="C1" s="229"/>
-      <c r="D1" s="229"/>
-      <c r="E1" s="229"/>
-      <c r="F1" s="229"/>
-      <c r="G1" s="229"/>
-      <c r="H1" s="229"/>
-      <c r="I1" s="229"/>
-      <c r="J1" s="229"/>
-      <c r="K1" s="229"/>
-      <c r="L1" s="229"/>
-      <c r="M1" s="229"/>
-      <c r="N1" s="229"/>
-      <c r="O1" s="229"/>
-      <c r="P1" s="229"/>
-      <c r="Q1" s="229"/>
-      <c r="R1" s="230"/>
+      <c r="B1" s="216"/>
+      <c r="C1" s="216"/>
+      <c r="D1" s="216"/>
+      <c r="E1" s="216"/>
+      <c r="F1" s="216"/>
+      <c r="G1" s="216"/>
+      <c r="H1" s="216"/>
+      <c r="I1" s="216"/>
+      <c r="J1" s="216"/>
+      <c r="K1" s="216"/>
+      <c r="L1" s="216"/>
+      <c r="M1" s="216"/>
+      <c r="N1" s="216"/>
+      <c r="O1" s="216"/>
+      <c r="P1" s="216"/>
+      <c r="Q1" s="216"/>
+      <c r="R1" s="217"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="94"/>
-      <c r="C2" s="198">
-        <v>1500000</v>
-      </c>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
-      <c r="K2" s="58"/>
+      <c r="A2" s="93"/>
+      <c r="C2" s="186">
+        <v>1822930.46</v>
+      </c>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
       <c r="L2" s="13"/>
       <c r="R2" s="6"/>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" s="90"/>
-      <c r="D3" s="198">
-        <v>400523.88</v>
-      </c>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="L3" s="92"/>
+      <c r="A3" s="89"/>
+      <c r="D3" s="186">
+        <v>358698.61</v>
+      </c>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="L3" s="91"/>
       <c r="R3" s="6"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="90"/>
+      <c r="A4" s="89"/>
       <c r="C4" s="13" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D4" s="13"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="L4" s="92"/>
-      <c r="M4" s="226"/>
-      <c r="N4" s="226"/>
-      <c r="O4" s="226"/>
-      <c r="P4" s="226"/>
-      <c r="Q4" s="226"/>
-      <c r="R4" s="227"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="L4" s="91"/>
+      <c r="M4" s="213"/>
+      <c r="N4" s="213"/>
+      <c r="O4" s="213"/>
+      <c r="P4" s="213"/>
+      <c r="Q4" s="213"/>
+      <c r="R4" s="214"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" s="90"/>
-      <c r="B5" s="93"/>
-      <c r="C5" s="236">
+      <c r="A5" s="89"/>
+      <c r="B5" s="92"/>
+      <c r="C5" s="223">
         <f>D3</f>
-        <v>400523.88</v>
-      </c>
-      <c r="D5" s="236"/>
+        <v>358698.61</v>
+      </c>
+      <c r="D5" s="223"/>
       <c r="E5" s="13"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="L5" s="92"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
+      <c r="L5" s="91"/>
       <c r="M5" s="17"/>
       <c r="R5" s="6"/>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A6" s="90"/>
+      <c r="A6" s="89"/>
       <c r="C6" s="13" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="13"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="58"/>
-      <c r="I6" s="58"/>
-      <c r="J6" s="58"/>
-      <c r="K6" s="58"/>
-      <c r="L6" s="58"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="57"/>
+      <c r="L6" s="57"/>
       <c r="R6" s="6"/>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" s="90"/>
-      <c r="B7" s="89"/>
-      <c r="C7" s="236">
+      <c r="A7" s="89"/>
+      <c r="B7" s="88"/>
+      <c r="C7" s="223">
         <f>C2-D3</f>
-        <v>1099476.1200000001</v>
-      </c>
-      <c r="D7" s="236"/>
-      <c r="E7" s="91"/>
-      <c r="G7" s="58"/>
-      <c r="H7" s="58"/>
-      <c r="I7" s="58"/>
-      <c r="J7" s="58"/>
-      <c r="K7" s="58"/>
-      <c r="L7" s="58"/>
+        <v>1464231.85</v>
+      </c>
+      <c r="D7" s="223"/>
+      <c r="E7" s="90"/>
+      <c r="G7" s="57"/>
+      <c r="H7" s="57"/>
+      <c r="I7" s="57"/>
+      <c r="J7" s="57"/>
+      <c r="K7" s="57"/>
+      <c r="L7" s="57"/>
       <c r="R7" s="6"/>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A8" s="90"/>
-      <c r="B8" s="89"/>
-      <c r="C8" s="89" t="s">
+      <c r="A8" s="89"/>
+      <c r="B8" s="88"/>
+      <c r="C8" s="88" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="89"/>
-      <c r="E8" s="89"/>
-      <c r="G8" s="58"/>
-      <c r="H8" s="58"/>
-      <c r="I8" s="58"/>
-      <c r="J8" s="58"/>
-      <c r="K8" s="58"/>
-      <c r="L8" s="58"/>
+      <c r="D8" s="88"/>
+      <c r="E8" s="88"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="57"/>
+      <c r="K8" s="57"/>
+      <c r="L8" s="57"/>
       <c r="R8" s="6"/>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" s="88"/>
-      <c r="B9" s="87"/>
-      <c r="C9" s="86"/>
-      <c r="D9" s="86"/>
-      <c r="E9" s="86"/>
-      <c r="F9" s="85"/>
-      <c r="G9" s="84"/>
-      <c r="H9" s="84"/>
-      <c r="I9" s="84"/>
-      <c r="J9" s="84"/>
-      <c r="K9" s="84"/>
-      <c r="L9" s="83"/>
+      <c r="A9" s="87"/>
+      <c r="B9" s="86"/>
+      <c r="C9" s="85"/>
+      <c r="D9" s="85"/>
+      <c r="E9" s="85"/>
+      <c r="F9" s="84"/>
+      <c r="G9" s="83"/>
+      <c r="H9" s="83"/>
+      <c r="I9" s="83"/>
+      <c r="J9" s="83"/>
+      <c r="K9" s="83"/>
+      <c r="L9" s="82"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -3090,1397 +3051,1393 @@
       <c r="R9" s="8"/>
     </row>
     <row r="10" spans="1:21" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="82" t="s">
+      <c r="A10" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="78" t="s">
+      <c r="B10" s="77" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="81" t="s">
+      <c r="C10" s="80" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="81" t="s">
+      <c r="D10" s="80" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="81" t="s">
+      <c r="E10" s="80" t="s">
         <v>29</v>
       </c>
-      <c r="F10" s="80" t="s">
+      <c r="F10" s="79" t="s">
         <v>28</v>
       </c>
-      <c r="G10" s="79" t="s">
-        <v>110</v>
-      </c>
-      <c r="H10" s="79" t="s">
+      <c r="G10" s="78" t="s">
+        <v>109</v>
+      </c>
+      <c r="H10" s="78" t="s">
         <v>27</v>
       </c>
-      <c r="I10" s="79" t="s">
+      <c r="I10" s="78" t="s">
         <v>26</v>
       </c>
-      <c r="J10" s="79" t="s">
+      <c r="J10" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="K10" s="79" t="s">
+      <c r="K10" s="78" t="s">
         <v>24</v>
       </c>
-      <c r="L10" s="79" t="s">
+      <c r="L10" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="M10" s="78" t="s">
-        <v>142</v>
-      </c>
-      <c r="N10" s="78" t="s">
+      <c r="M10" s="77" t="s">
+        <v>141</v>
+      </c>
+      <c r="N10" s="77" t="s">
         <v>22</v>
       </c>
-      <c r="O10" s="78" t="s">
-        <v>160</v>
-      </c>
-      <c r="P10" s="78" t="s">
+      <c r="O10" s="77" t="s">
+        <v>157</v>
+      </c>
+      <c r="P10" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="Q10" s="78" t="s">
+      <c r="Q10" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="R10" s="78" t="s">
+      <c r="R10" s="77" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:21" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="188" t="s">
+      <c r="A11" s="177" t="s">
         <v>81</v>
       </c>
-      <c r="B11" s="189"/>
-      <c r="C11" s="190" t="s">
+      <c r="B11" s="178"/>
+      <c r="C11" s="179" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="191" t="s">
+      <c r="D11" s="180" t="s">
         <v>100</v>
       </c>
-      <c r="E11" s="166"/>
-      <c r="F11" s="192">
+      <c r="E11" s="165"/>
+      <c r="F11" s="181">
         <v>7.9</v>
       </c>
-      <c r="G11" s="69">
-        <v>126962.6326855146</v>
-      </c>
-      <c r="H11" s="69">
-        <v>0</v>
-      </c>
-      <c r="I11" s="69">
+      <c r="G11" s="68">
+        <v>118500.00000000001</v>
+      </c>
+      <c r="H11" s="68">
+        <v>0</v>
+      </c>
+      <c r="I11" s="68">
         <f>G11</f>
-        <v>126962.6326855146</v>
-      </c>
-      <c r="J11" s="69" t="e">
+        <v>118500.00000000001</v>
+      </c>
+      <c r="J11" s="68" t="e">
         <f>C8*F11/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K11" s="69">
+      <c r="K11" s="68">
         <f t="shared" ref="K11:K18" si="0">G11-H11-I11</f>
         <v>0</v>
       </c>
-      <c r="L11" s="69"/>
-      <c r="M11" s="193">
+      <c r="L11" s="68"/>
+      <c r="M11" s="182">
         <f>(K11+L11)*3%</f>
         <v>0</v>
       </c>
-      <c r="N11" s="193">
+      <c r="N11" s="182">
         <f t="shared" ref="N11:N19" si="1">K11+M11+L11</f>
         <v>0</v>
       </c>
-      <c r="O11" s="69">
+      <c r="O11" s="68">
         <f>C$7*F11/100</f>
-        <v>86858.613480000015</v>
-      </c>
-      <c r="P11" s="69">
+        <v>115674.31615000003</v>
+      </c>
+      <c r="P11" s="68">
         <f t="shared" ref="P11:P30" si="2">C$9*F11/100</f>
         <v>0</v>
       </c>
-      <c r="Q11" s="69">
+      <c r="Q11" s="68">
         <f>C$5*F11/100</f>
-        <v>31641.386520000004</v>
-      </c>
-      <c r="R11" s="193">
+        <v>28337.190189999998</v>
+      </c>
+      <c r="R11" s="182">
         <f t="shared" ref="R11:R29" si="3">O11+N11+P11+Q11</f>
+        <v>144011.50634000002</v>
+      </c>
+      <c r="U11" s="94" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="170" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" s="163"/>
+      <c r="C12" s="171" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" s="172" t="s">
+        <v>101</v>
+      </c>
+      <c r="E12" s="173"/>
+      <c r="F12" s="174">
+        <v>7.9</v>
+      </c>
+      <c r="G12" s="161">
         <v>118500.00000000001</v>
       </c>
-      <c r="U11" s="95" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="171" t="s">
-        <v>82</v>
-      </c>
-      <c r="B12" s="164"/>
-      <c r="C12" s="172" t="s">
-        <v>35</v>
-      </c>
-      <c r="D12" s="173" t="s">
-        <v>101</v>
-      </c>
-      <c r="E12" s="174"/>
-      <c r="F12" s="175">
-        <v>7.9</v>
-      </c>
-      <c r="G12" s="162">
-        <v>130776.40741994916</v>
-      </c>
-      <c r="H12" s="162">
-        <v>0</v>
-      </c>
-      <c r="I12" s="69">
+      <c r="H12" s="161">
+        <v>0</v>
+      </c>
+      <c r="I12" s="68">
         <f>G12</f>
-        <v>130776.40741994916</v>
-      </c>
-      <c r="J12" s="162" t="e">
+        <v>118500.00000000001</v>
+      </c>
+      <c r="J12" s="161" t="e">
         <f>C8*F12/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K12" s="162">
+      <c r="K12" s="161">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L12" s="162"/>
-      <c r="M12" s="168">
+      <c r="L12" s="161"/>
+      <c r="M12" s="167">
         <f t="shared" ref="M12:M29" si="4">(K12+L12)*3%</f>
         <v>0</v>
       </c>
-      <c r="N12" s="168">
+      <c r="N12" s="167">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O12" s="162">
+      <c r="O12" s="161">
         <f t="shared" ref="O12:O29" si="5">C$7*F12/100</f>
-        <v>86858.613480000015</v>
-      </c>
-      <c r="P12" s="162">
+        <v>115674.31615000003</v>
+      </c>
+      <c r="P12" s="161">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q12" s="69">
+      <c r="Q12" s="68">
         <f t="shared" ref="Q12:Q22" si="6">C$5*F12/100</f>
-        <v>31641.386520000004</v>
-      </c>
-      <c r="R12" s="168">
+        <v>28337.190189999998</v>
+      </c>
+      <c r="R12" s="167">
         <f t="shared" si="3"/>
-        <v>118500.00000000001</v>
-      </c>
-      <c r="U12" s="96" t="s">
+        <v>144011.50634000002</v>
+      </c>
+      <c r="U12" s="95" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="176" t="s">
+      <c r="A13" s="162" t="s">
         <v>83</v>
       </c>
-      <c r="B13" s="177"/>
-      <c r="C13" s="178" t="s">
+      <c r="B13" s="163"/>
+      <c r="C13" s="96" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="185" t="s">
+      <c r="D13" s="164" t="s">
         <v>102</v>
       </c>
-      <c r="E13" s="180" t="s">
-        <v>111</v>
-      </c>
-      <c r="F13" s="186">
+      <c r="E13" s="165" t="s">
+        <v>110</v>
+      </c>
+      <c r="F13" s="166">
         <v>7.9</v>
       </c>
-      <c r="G13" s="182">
-        <v>512770.09664126451</v>
-      </c>
-      <c r="H13" s="183">
-        <v>0</v>
-      </c>
-      <c r="I13" s="182"/>
-      <c r="J13" s="183" t="e">
+      <c r="G13" s="68">
+        <v>646653.19954050251</v>
+      </c>
+      <c r="H13" s="161">
+        <v>0</v>
+      </c>
+      <c r="I13" s="68">
+        <f>300000+133890+212770</f>
+        <v>646660</v>
+      </c>
+      <c r="J13" s="161" t="e">
         <f>C8*F13/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K13" s="183">
+      <c r="K13" s="161">
         <f t="shared" si="0"/>
-        <v>512770.09664126451</v>
-      </c>
-      <c r="L13" s="183"/>
-      <c r="M13" s="184">
+        <v>-6.8004594974918291</v>
+      </c>
+      <c r="L13" s="161"/>
+      <c r="M13" s="167">
         <f t="shared" si="4"/>
-        <v>15383.102899237934</v>
-      </c>
-      <c r="N13" s="184">
+        <v>-0.20401378492475486</v>
+      </c>
+      <c r="N13" s="167">
         <f t="shared" si="1"/>
-        <v>528153.19954050239</v>
-      </c>
-      <c r="O13" s="183">
+        <v>-7.0044732824165843</v>
+      </c>
+      <c r="O13" s="161">
         <f t="shared" si="5"/>
-        <v>86858.613480000015</v>
-      </c>
-      <c r="P13" s="183">
+        <v>115674.31615000003</v>
+      </c>
+      <c r="P13" s="161">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q13" s="182">
+      <c r="Q13" s="68">
         <f t="shared" si="6"/>
-        <v>31641.386520000004</v>
-      </c>
-      <c r="R13" s="184">
+        <v>28337.190189999998</v>
+      </c>
+      <c r="R13" s="167">
         <f t="shared" si="3"/>
-        <v>646653.19954050251</v>
-      </c>
-      <c r="U13" s="96" t="s">
+        <v>144004.50186671762</v>
+      </c>
+      <c r="U13" s="95" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="113" t="s">
+      <c r="A14" s="112" t="s">
         <v>84</v>
       </c>
-      <c r="B14" s="77"/>
-      <c r="C14" s="96" t="s">
+      <c r="B14" s="76"/>
+      <c r="C14" s="95" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="159" t="s">
+      <c r="D14" s="158" t="s">
         <v>103</v>
       </c>
-      <c r="E14" s="116"/>
-      <c r="F14" s="98">
+      <c r="E14" s="115"/>
+      <c r="F14" s="97">
         <v>7.9</v>
       </c>
-      <c r="G14" s="161">
-        <v>147838.03123189326</v>
-      </c>
-      <c r="H14" s="76"/>
-      <c r="I14" s="69">
-        <f>G14+2</f>
-        <v>147840.03123189326</v>
-      </c>
-      <c r="J14" s="67" t="e">
+      <c r="G14" s="160">
+        <v>118497.94000000002</v>
+      </c>
+      <c r="H14" s="75"/>
+      <c r="I14" s="68">
+        <f>G14</f>
+        <v>118497.94000000002</v>
+      </c>
+      <c r="J14" s="66" t="e">
         <f>C8*F14/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K14" s="67">
+      <c r="K14" s="66">
         <f t="shared" si="0"/>
-        <v>-2</v>
-      </c>
-      <c r="L14" s="68"/>
-      <c r="M14" s="66">
+        <v>0</v>
+      </c>
+      <c r="L14" s="67"/>
+      <c r="M14" s="65">
         <f t="shared" si="4"/>
-        <v>-0.06</v>
-      </c>
-      <c r="N14" s="66">
+        <v>0</v>
+      </c>
+      <c r="N14" s="65">
         <f t="shared" si="1"/>
-        <v>-2.06</v>
-      </c>
-      <c r="O14" s="67">
+        <v>0</v>
+      </c>
+      <c r="O14" s="66">
         <f t="shared" si="5"/>
-        <v>86858.613480000015</v>
-      </c>
-      <c r="P14" s="67">
+        <v>115674.31615000003</v>
+      </c>
+      <c r="P14" s="66">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q14" s="69">
+      <c r="Q14" s="68">
         <f t="shared" si="6"/>
-        <v>31641.386520000004</v>
-      </c>
-      <c r="R14" s="66">
+        <v>28337.190189999998</v>
+      </c>
+      <c r="R14" s="65">
         <f t="shared" si="3"/>
-        <v>118497.94000000002</v>
-      </c>
-      <c r="U14" s="96" t="s">
+        <v>144011.50634000002</v>
+      </c>
+      <c r="U14" s="95" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="113" t="s">
+      <c r="A15" s="112" t="s">
         <v>85</v>
       </c>
-      <c r="B15" s="73"/>
-      <c r="C15" s="96" t="s">
+      <c r="B15" s="72"/>
+      <c r="C15" s="95" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="114" t="s">
+      <c r="D15" s="113" t="s">
         <v>104</v>
       </c>
-      <c r="E15" s="116"/>
-      <c r="F15" s="98">
+      <c r="E15" s="115"/>
+      <c r="F15" s="97">
         <v>7.9</v>
       </c>
-      <c r="G15" s="74">
-        <v>210671.45988465688</v>
-      </c>
-      <c r="H15" s="76">
-        <v>0</v>
-      </c>
-      <c r="I15" s="69">
-        <f>112320-G27</f>
-        <v>102700</v>
-      </c>
-      <c r="J15" s="67" t="e">
+      <c r="G15" s="73">
+        <v>229710.6036811966</v>
+      </c>
+      <c r="H15" s="75">
+        <v>0</v>
+      </c>
+      <c r="I15" s="68">
+        <f>237847-G27</f>
+        <v>229710.876712</v>
+      </c>
+      <c r="J15" s="66" t="e">
         <f>C8*F15/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K15" s="67">
+      <c r="K15" s="66">
         <f t="shared" si="0"/>
-        <v>107971.45988465688</v>
-      </c>
-      <c r="L15" s="67"/>
-      <c r="M15" s="66">
+        <v>-0.27303080339333974</v>
+      </c>
+      <c r="L15" s="66"/>
+      <c r="M15" s="65">
         <f t="shared" si="4"/>
-        <v>3239.1437965397063</v>
-      </c>
-      <c r="N15" s="66">
+        <v>-8.190924101800192E-3</v>
+      </c>
+      <c r="N15" s="65">
         <f t="shared" si="1"/>
-        <v>111210.60368119659</v>
-      </c>
-      <c r="O15" s="67">
+        <v>-0.28122172749513991</v>
+      </c>
+      <c r="O15" s="66">
         <f t="shared" si="5"/>
-        <v>86858.613480000015</v>
-      </c>
-      <c r="P15" s="67">
+        <v>115674.31615000003</v>
+      </c>
+      <c r="P15" s="66">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q15" s="69">
+      <c r="Q15" s="68">
         <f t="shared" si="6"/>
-        <v>31641.386520000004</v>
-      </c>
-      <c r="R15" s="66">
+        <v>28337.190189999998</v>
+      </c>
+      <c r="R15" s="65">
         <f t="shared" si="3"/>
-        <v>229710.6036811966</v>
-      </c>
-      <c r="U15" s="96" t="s">
+        <v>144011.22511827253</v>
+      </c>
+      <c r="U15" s="95" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="176" t="s">
+      <c r="A16" s="162" t="s">
         <v>86</v>
       </c>
-      <c r="B16" s="177"/>
-      <c r="C16" s="178" t="s">
+      <c r="B16" s="163"/>
+      <c r="C16" s="96" t="s">
         <v>39</v>
       </c>
-      <c r="D16" s="185" t="s">
-        <v>105</v>
-      </c>
-      <c r="E16" s="180"/>
-      <c r="F16" s="186">
+      <c r="D16" s="164" t="s">
+        <v>165</v>
+      </c>
+      <c r="E16" s="165"/>
+      <c r="F16" s="166">
         <v>7.9</v>
       </c>
-      <c r="G16" s="182">
-        <v>685819.71349992836</v>
-      </c>
-      <c r="H16" s="183">
-        <v>0</v>
-      </c>
-      <c r="I16" s="182"/>
-      <c r="J16" s="183" t="e">
+      <c r="G16" s="68">
+        <v>824894.30490492634</v>
+      </c>
+      <c r="H16" s="161">
+        <v>0</v>
+      </c>
+      <c r="I16" s="68">
+        <f>888825-I28</f>
+        <v>824894.08915568655</v>
+      </c>
+      <c r="J16" s="161" t="e">
         <f>C8*F16/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K16" s="183">
+      <c r="K16" s="161">
         <f t="shared" si="0"/>
-        <v>685819.71349992836</v>
-      </c>
-      <c r="L16" s="183"/>
-      <c r="M16" s="184">
+        <v>0.21574923978187144</v>
+      </c>
+      <c r="L16" s="161"/>
+      <c r="M16" s="167">
         <f t="shared" si="4"/>
-        <v>20574.591404997849</v>
-      </c>
-      <c r="N16" s="184">
+        <v>6.4724771934561425E-3</v>
+      </c>
+      <c r="N16" s="167">
         <f t="shared" si="1"/>
-        <v>706394.30490492622</v>
-      </c>
-      <c r="O16" s="183">
+        <v>0.22222171697532758</v>
+      </c>
+      <c r="O16" s="161">
         <f t="shared" si="5"/>
-        <v>86858.613480000015</v>
-      </c>
-      <c r="P16" s="183">
+        <v>115674.31615000003</v>
+      </c>
+      <c r="P16" s="161">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q16" s="182">
+      <c r="Q16" s="68">
         <f t="shared" si="6"/>
-        <v>31641.386520000004</v>
-      </c>
-      <c r="R16" s="184">
+        <v>28337.190189999998</v>
+      </c>
+      <c r="R16" s="167">
         <f t="shared" si="3"/>
-        <v>824894.30490492634</v>
-      </c>
-      <c r="U16" s="96" t="s">
+        <v>144011.728561717</v>
+      </c>
+      <c r="U16" s="95" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="113" t="s">
+      <c r="A17" s="112" t="s">
         <v>87</v>
       </c>
-      <c r="B17" s="73"/>
-      <c r="C17" s="96" t="s">
+      <c r="B17" s="72"/>
+      <c r="C17" s="95" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="114" t="s">
-        <v>106</v>
-      </c>
-      <c r="E17" s="116" t="s">
-        <v>147</v>
-      </c>
-      <c r="F17" s="98">
+      <c r="D17" s="113" t="s">
+        <v>105</v>
+      </c>
+      <c r="E17" s="115" t="s">
+        <v>146</v>
+      </c>
+      <c r="F17" s="97">
         <v>7.9</v>
       </c>
-      <c r="G17" s="74">
-        <v>128969.88254574331</v>
-      </c>
-      <c r="H17" s="67">
-        <v>0</v>
-      </c>
-      <c r="I17" s="69">
-        <f>112320-I23</f>
-        <v>102700</v>
-      </c>
-      <c r="J17" s="67" t="e">
+      <c r="G17" s="73">
+        <v>145557.97902211564</v>
+      </c>
+      <c r="H17" s="66">
+        <v>0</v>
+      </c>
+      <c r="I17" s="68">
+        <f>145554-I23</f>
+        <v>137417.876712</v>
+      </c>
+      <c r="J17" s="66" t="e">
         <f>C8*F17/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K17" s="67">
+      <c r="K17" s="66">
         <f t="shared" si="0"/>
-        <v>26269.882545743312</v>
-      </c>
-      <c r="L17" s="67"/>
-      <c r="M17" s="66">
+        <v>8140.1023101156461</v>
+      </c>
+      <c r="L17" s="66"/>
+      <c r="M17" s="65">
         <f t="shared" si="4"/>
-        <v>788.09647637229932</v>
-      </c>
-      <c r="N17" s="66">
+        <v>244.20306930346936</v>
+      </c>
+      <c r="N17" s="65">
         <f t="shared" si="1"/>
-        <v>27057.979022115611</v>
-      </c>
-      <c r="O17" s="67">
+        <v>8384.3053794191146</v>
+      </c>
+      <c r="O17" s="66">
         <f t="shared" si="5"/>
-        <v>86858.613480000015</v>
-      </c>
-      <c r="P17" s="67">
+        <v>115674.31615000003</v>
+      </c>
+      <c r="P17" s="66">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q17" s="69">
+      <c r="Q17" s="68">
         <f t="shared" si="6"/>
-        <v>31641.386520000004</v>
-      </c>
-      <c r="R17" s="66">
+        <v>28337.190189999998</v>
+      </c>
+      <c r="R17" s="65">
         <f t="shared" si="3"/>
-        <v>145557.97902211564</v>
-      </c>
-      <c r="U17" s="96" t="s">
+        <v>152395.81171941914</v>
+      </c>
+      <c r="U17" s="95" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="163" t="s">
+      <c r="A18" s="162" t="s">
         <v>88</v>
       </c>
-      <c r="B18" s="164"/>
-      <c r="C18" s="97" t="s">
+      <c r="B18" s="163"/>
+      <c r="C18" s="96" t="s">
         <v>41</v>
       </c>
-      <c r="D18" s="165" t="s">
-        <v>149</v>
-      </c>
-      <c r="E18" s="166" t="s">
+      <c r="D18" s="164" t="s">
         <v>148</v>
       </c>
-      <c r="F18" s="167">
+      <c r="E18" s="165" t="s">
+        <v>147</v>
+      </c>
+      <c r="F18" s="166">
         <v>7.9</v>
       </c>
-      <c r="G18" s="69">
-        <v>453792.3238377446</v>
-      </c>
-      <c r="H18" s="162">
-        <v>0</v>
-      </c>
-      <c r="I18" s="69">
-        <f>305000-I26</f>
-        <v>264434.68</v>
-      </c>
-      <c r="J18" s="162" t="e">
+      <c r="G18" s="68">
+        <v>313538.37315287697</v>
+      </c>
+      <c r="H18" s="161">
+        <v>0</v>
+      </c>
+      <c r="I18" s="68"/>
+      <c r="J18" s="161" t="e">
         <f>C8*F18/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K18" s="162">
+      <c r="K18" s="161">
         <f t="shared" si="0"/>
-        <v>189357.6438377446</v>
-      </c>
-      <c r="L18" s="162"/>
-      <c r="M18" s="168">
+        <v>313538.37315287697</v>
+      </c>
+      <c r="L18" s="161"/>
+      <c r="M18" s="167">
         <f t="shared" si="4"/>
-        <v>5680.7293151323374</v>
-      </c>
-      <c r="N18" s="168">
+        <v>9406.1511945863094</v>
+      </c>
+      <c r="N18" s="167">
         <f t="shared" si="1"/>
-        <v>195038.37315287694</v>
-      </c>
-      <c r="O18" s="162">
+        <v>322944.52434746327</v>
+      </c>
+      <c r="O18" s="161">
         <f t="shared" si="5"/>
-        <v>86858.613480000015</v>
-      </c>
-      <c r="P18" s="162">
+        <v>115674.31615000003</v>
+      </c>
+      <c r="P18" s="161">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q18" s="69">
+      <c r="Q18" s="68">
         <f t="shared" si="6"/>
-        <v>31641.386520000004</v>
-      </c>
-      <c r="R18" s="168">
+        <v>28337.190189999998</v>
+      </c>
+      <c r="R18" s="167">
         <f t="shared" si="3"/>
-        <v>313538.37315287697</v>
-      </c>
-      <c r="U18" s="96" t="s">
+        <v>466956.0306874633</v>
+      </c>
+      <c r="U18" s="95" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="163" t="s">
+      <c r="A19" s="162" t="s">
         <v>89</v>
       </c>
-      <c r="B19" s="164"/>
-      <c r="C19" s="97" t="s">
+      <c r="B19" s="163"/>
+      <c r="C19" s="96" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="165" t="s">
-        <v>107</v>
-      </c>
-      <c r="E19" s="166"/>
-      <c r="F19" s="167">
+      <c r="D19" s="164" t="s">
+        <v>106</v>
+      </c>
+      <c r="E19" s="165"/>
+      <c r="F19" s="166">
         <v>7.9</v>
       </c>
-      <c r="G19" s="69">
-        <v>121543.05806289706</v>
-      </c>
-      <c r="H19" s="162">
-        <v>0</v>
-      </c>
-      <c r="I19" s="69">
-        <v>122000</v>
-      </c>
-      <c r="J19" s="162" t="e">
+      <c r="G19" s="68">
+        <v>117558.69960956796</v>
+      </c>
+      <c r="H19" s="161">
+        <v>0</v>
+      </c>
+      <c r="I19" s="68">
+        <f>116620</f>
+        <v>116620</v>
+      </c>
+      <c r="J19" s="161" t="e">
         <f>C8*F19/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K19" s="162">
+      <c r="K19" s="161">
         <f t="shared" ref="K19:K29" si="7">G19-H19-I19</f>
-        <v>-456.94193710293621</v>
-      </c>
-      <c r="L19" s="162">
+        <v>938.69960956796422</v>
+      </c>
+      <c r="L19" s="161">
         <f>G19-I19</f>
-        <v>-456.94193710293621</v>
-      </c>
-      <c r="M19" s="168">
+        <v>938.69960956796422</v>
+      </c>
+      <c r="M19" s="167">
         <f t="shared" si="4"/>
-        <v>-27.416516226176171</v>
-      </c>
-      <c r="N19" s="168">
+        <v>56.321976574077851</v>
+      </c>
+      <c r="N19" s="167">
         <f t="shared" si="1"/>
-        <v>-941.30039043204852</v>
-      </c>
-      <c r="O19" s="162">
+        <v>1933.7211957100062</v>
+      </c>
+      <c r="O19" s="161">
         <f t="shared" si="5"/>
-        <v>86858.613480000015</v>
-      </c>
-      <c r="P19" s="162">
+        <v>115674.31615000003</v>
+      </c>
+      <c r="P19" s="161">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q19" s="69">
+      <c r="Q19" s="68">
         <f t="shared" si="6"/>
-        <v>31641.386520000004</v>
-      </c>
-      <c r="R19" s="168">
+        <v>28337.190189999998</v>
+      </c>
+      <c r="R19" s="167">
         <f t="shared" si="3"/>
-        <v>117558.69960956796</v>
-      </c>
-      <c r="U19" s="96" t="s">
+        <v>145945.22753571003</v>
+      </c>
+      <c r="U19" s="95" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="113" t="s">
+      <c r="A20" s="112" t="s">
         <v>90</v>
       </c>
-      <c r="B20" s="73"/>
-      <c r="C20" s="96" t="s">
+      <c r="B20" s="72"/>
+      <c r="C20" s="95" t="s">
         <v>43</v>
       </c>
-      <c r="D20" s="114" t="s">
+      <c r="D20" s="113" t="s">
+        <v>107</v>
+      </c>
+      <c r="E20" s="115"/>
+      <c r="F20" s="97">
+        <v>7.9</v>
+      </c>
+      <c r="G20" s="73">
+        <v>147005.20617134054</v>
+      </c>
+      <c r="H20" s="66"/>
+      <c r="I20" s="68">
+        <f>G20</f>
+        <v>147005.20617134054</v>
+      </c>
+      <c r="J20" s="66"/>
+      <c r="K20" s="66">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="66"/>
+      <c r="M20" s="65">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N20" s="65">
+        <f t="shared" ref="N20:N29" si="8">K20+M20+L20</f>
+        <v>0</v>
+      </c>
+      <c r="O20" s="66">
+        <f t="shared" si="5"/>
+        <v>115674.31615000003</v>
+      </c>
+      <c r="P20" s="66">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q20" s="68">
+        <f t="shared" si="6"/>
+        <v>28337.190189999998</v>
+      </c>
+      <c r="R20" s="65">
+        <f t="shared" si="3"/>
+        <v>144011.50634000002</v>
+      </c>
+      <c r="U20" s="95" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="162" t="s">
+        <v>91</v>
+      </c>
+      <c r="B21" s="163"/>
+      <c r="C21" s="96" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" s="164" t="s">
         <v>108</v>
       </c>
-      <c r="E20" s="116"/>
-      <c r="F20" s="98">
+      <c r="E21" s="165" t="s">
+        <v>111</v>
+      </c>
+      <c r="F21" s="166">
         <v>7.9</v>
       </c>
-      <c r="G20" s="74">
-        <v>130374.95744790341</v>
-      </c>
-      <c r="H20" s="67"/>
-      <c r="I20" s="69">
-        <f>102700</f>
-        <v>102700</v>
-      </c>
-      <c r="J20" s="67"/>
-      <c r="K20" s="67">
+      <c r="G21" s="68">
+        <v>118500.17984677525</v>
+      </c>
+      <c r="H21" s="161"/>
+      <c r="I21" s="68"/>
+      <c r="J21" s="161"/>
+      <c r="K21" s="161">
         <f t="shared" si="7"/>
-        <v>27674.957447903405</v>
-      </c>
-      <c r="L20" s="67"/>
-      <c r="M20" s="66">
+        <v>118500.17984677525</v>
+      </c>
+      <c r="L21" s="161"/>
+      <c r="M21" s="167">
         <f t="shared" si="4"/>
-        <v>830.24872343710217</v>
-      </c>
-      <c r="N20" s="66">
-        <f t="shared" ref="N20:N29" si="8">K20+M20+L20</f>
-        <v>28505.206171340509</v>
-      </c>
-      <c r="O20" s="67">
+        <v>3555.0053954032574</v>
+      </c>
+      <c r="N21" s="167">
+        <f t="shared" si="8"/>
+        <v>122055.18524217852</v>
+      </c>
+      <c r="O21" s="161">
         <f t="shared" si="5"/>
-        <v>86858.613480000015</v>
-      </c>
-      <c r="P20" s="67">
+        <v>115674.31615000003</v>
+      </c>
+      <c r="P21" s="161">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q20" s="69">
+      <c r="Q21" s="68">
         <f t="shared" si="6"/>
-        <v>31641.386520000004</v>
-      </c>
-      <c r="R20" s="66">
+        <v>28337.190189999998</v>
+      </c>
+      <c r="R21" s="167">
         <f t="shared" si="3"/>
-        <v>147005.20617134054</v>
-      </c>
-      <c r="U20" s="96" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="163" t="s">
-        <v>91</v>
-      </c>
-      <c r="B21" s="164"/>
-      <c r="C21" s="97" t="s">
+        <v>266066.69158217852</v>
+      </c>
+      <c r="U21" s="95" t="s">
         <v>44</v>
       </c>
-      <c r="D21" s="165" t="s">
-        <v>109</v>
-      </c>
-      <c r="E21" s="166" t="s">
-        <v>112</v>
-      </c>
-      <c r="F21" s="167">
+    </row>
+    <row r="22" spans="1:21" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="162" t="s">
+        <v>92</v>
+      </c>
+      <c r="B22" s="163"/>
+      <c r="C22" s="96" t="s">
+        <v>45</v>
+      </c>
+      <c r="D22" s="164" t="s">
+        <v>155</v>
+      </c>
+      <c r="E22" s="165" t="s">
+        <v>154</v>
+      </c>
+      <c r="F22" s="166">
         <v>7.9</v>
       </c>
-      <c r="G21" s="69">
-        <v>496576.85460851964</v>
-      </c>
-      <c r="H21" s="162"/>
-      <c r="I21" s="69">
-        <f>537142-I24</f>
-        <v>496576.68</v>
-      </c>
-      <c r="J21" s="162"/>
-      <c r="K21" s="162">
+      <c r="G22" s="68">
+        <v>118500.00000000001</v>
+      </c>
+      <c r="H22" s="161"/>
+      <c r="I22" s="68">
+        <f>G22</f>
+        <v>118500.00000000001</v>
+      </c>
+      <c r="J22" s="161"/>
+      <c r="K22" s="161">
         <f t="shared" si="7"/>
-        <v>0.17460851965006441</v>
-      </c>
-      <c r="L21" s="162"/>
-      <c r="M21" s="168">
+        <v>0</v>
+      </c>
+      <c r="L22" s="161"/>
+      <c r="M22" s="167">
         <f t="shared" si="4"/>
-        <v>5.2382555895019323E-3</v>
-      </c>
-      <c r="N21" s="168">
+        <v>0</v>
+      </c>
+      <c r="N22" s="167">
         <f t="shared" si="8"/>
-        <v>0.17984677523956635</v>
-      </c>
-      <c r="O21" s="162">
+        <v>0</v>
+      </c>
+      <c r="O22" s="161">
         <f t="shared" si="5"/>
-        <v>86858.613480000015</v>
-      </c>
-      <c r="P21" s="162">
+        <v>115674.31615000003</v>
+      </c>
+      <c r="P22" s="161">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q21" s="69">
+      <c r="Q22" s="68">
         <f t="shared" si="6"/>
-        <v>31641.386520000004</v>
-      </c>
-      <c r="R21" s="168">
+        <v>28337.190189999998</v>
+      </c>
+      <c r="R22" s="167">
         <f t="shared" si="3"/>
-        <v>118500.17984677525</v>
-      </c>
-      <c r="U21" s="96" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="163" t="s">
-        <v>92</v>
-      </c>
-      <c r="B22" s="164"/>
-      <c r="C22" s="97" t="s">
+        <v>144011.50634000002</v>
+      </c>
+      <c r="S22" s="183"/>
+      <c r="U22" s="95" t="s">
         <v>45</v>
       </c>
-      <c r="D22" s="165" t="s">
-        <v>157</v>
-      </c>
-      <c r="E22" s="166" t="s">
-        <v>156</v>
-      </c>
-      <c r="F22" s="167">
-        <v>7.9</v>
-      </c>
-      <c r="G22" s="69">
-        <v>653629.44749144034</v>
-      </c>
-      <c r="H22" s="162"/>
-      <c r="I22" s="69">
-        <f>G22</f>
-        <v>653629.44749144034</v>
-      </c>
-      <c r="J22" s="162"/>
-      <c r="K22" s="162">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L22" s="162"/>
-      <c r="M22" s="168">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="N22" s="168">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O22" s="162">
-        <f t="shared" si="5"/>
-        <v>86858.613480000015</v>
-      </c>
-      <c r="P22" s="162">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q22" s="69">
-        <f t="shared" si="6"/>
-        <v>31641.386520000004</v>
-      </c>
-      <c r="R22" s="168">
-        <f t="shared" si="3"/>
-        <v>118500.00000000001</v>
-      </c>
-      <c r="S22" s="194"/>
-      <c r="U22" s="96" t="s">
-        <v>45</v>
-      </c>
     </row>
     <row r="23" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="113"/>
-      <c r="B23" s="73"/>
-      <c r="C23" s="96" t="s">
+      <c r="A23" s="112"/>
+      <c r="B23" s="72"/>
+      <c r="C23" s="95" t="s">
         <v>93</v>
       </c>
-      <c r="D23" s="115" t="str">
+      <c r="D23" s="114" t="str">
         <f>D17</f>
         <v>Estevez Norberto Omar</v>
       </c>
-      <c r="E23" s="116" t="s">
-        <v>147</v>
-      </c>
-      <c r="F23" s="98">
+      <c r="E23" s="115" t="s">
+        <v>146</v>
+      </c>
+      <c r="F23" s="97">
         <v>0.74</v>
       </c>
-      <c r="G23" s="74">
-        <v>9619.9999999999982</v>
-      </c>
-      <c r="H23" s="67"/>
-      <c r="I23" s="69">
+      <c r="G23" s="73">
+        <v>8136.1232879999998</v>
+      </c>
+      <c r="H23" s="66"/>
+      <c r="I23" s="68">
         <f>G23</f>
-        <v>9619.9999999999982</v>
-      </c>
-      <c r="J23" s="67"/>
-      <c r="K23" s="67">
+        <v>8136.1232879999998</v>
+      </c>
+      <c r="J23" s="66"/>
+      <c r="K23" s="66">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="L23" s="67"/>
-      <c r="M23" s="66">
+      <c r="L23" s="66"/>
+      <c r="M23" s="65">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N23" s="66">
+      <c r="N23" s="65">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="O23" s="67">
+      <c r="O23" s="66">
         <f t="shared" si="5"/>
-        <v>8136.1232879999998</v>
-      </c>
-      <c r="P23" s="67">
+        <v>10835.315690000001</v>
+      </c>
+      <c r="P23" s="66">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q23" s="67"/>
-      <c r="R23" s="66">
+      <c r="Q23" s="66"/>
+      <c r="R23" s="65">
         <f t="shared" si="3"/>
-        <v>8136.1232879999998</v>
-      </c>
-      <c r="U23" s="96" t="s">
+        <v>10835.315690000001</v>
+      </c>
+      <c r="U23" s="95" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="24" spans="1:21" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="163"/>
-      <c r="B24" s="164"/>
-      <c r="C24" s="97" t="s">
+      <c r="A24" s="162"/>
+      <c r="B24" s="163"/>
+      <c r="C24" s="96" t="s">
         <v>94</v>
       </c>
-      <c r="D24" s="169" t="str">
+      <c r="D24" s="168" t="str">
         <f>D21</f>
         <v>Moro Vanesa Yania / Juan Carlos Moro</v>
       </c>
-      <c r="E24" s="166" t="s">
-        <v>112</v>
-      </c>
-      <c r="F24" s="167">
+      <c r="E24" s="165" t="s">
+        <v>111</v>
+      </c>
+      <c r="F24" s="166">
         <v>0.74</v>
       </c>
-      <c r="G24" s="69">
-        <v>40565.32</v>
-      </c>
-      <c r="H24" s="162"/>
-      <c r="I24" s="69">
-        <f>G24</f>
-        <v>40565.32</v>
-      </c>
-      <c r="J24" s="162"/>
-      <c r="K24" s="162">
+      <c r="G24" s="68">
+        <v>8136.1232879999998</v>
+      </c>
+      <c r="H24" s="161"/>
+      <c r="I24" s="68"/>
+      <c r="J24" s="161"/>
+      <c r="K24" s="161">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L24" s="162"/>
-      <c r="M24" s="168">
+        <v>8136.1232879999998</v>
+      </c>
+      <c r="L24" s="161"/>
+      <c r="M24" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="N24" s="168">
+        <v>244.08369863999999</v>
+      </c>
+      <c r="N24" s="167">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O24" s="162">
+        <v>8380.2069866399997</v>
+      </c>
+      <c r="O24" s="161">
         <f t="shared" si="5"/>
-        <v>8136.1232879999998</v>
-      </c>
-      <c r="P24" s="162">
+        <v>10835.315690000001</v>
+      </c>
+      <c r="P24" s="161">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q24" s="162">
+      <c r="Q24" s="161">
         <f>'Calculo Servicios  (2)'!H22</f>
         <v>0</v>
       </c>
-      <c r="R24" s="168">
+      <c r="R24" s="167">
         <f t="shared" si="3"/>
-        <v>8136.1232879999998</v>
-      </c>
-      <c r="U24" s="96" t="s">
+        <v>19215.522676640001</v>
+      </c>
+      <c r="U24" s="95" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="113"/>
-      <c r="B25" s="73"/>
-      <c r="C25" s="96" t="s">
+      <c r="A25" s="112"/>
+      <c r="B25" s="72"/>
+      <c r="C25" s="95" t="s">
         <v>95</v>
       </c>
-      <c r="D25" s="115" t="str">
+      <c r="D25" s="114" t="str">
         <f>D20</f>
         <v>Scarlercio Jorge Omar</v>
       </c>
-      <c r="E25" s="115"/>
-      <c r="F25" s="98">
+      <c r="E25" s="114"/>
+      <c r="F25" s="97">
         <v>0.74</v>
       </c>
-      <c r="G25" s="74">
-        <v>9619.9999999999982</v>
-      </c>
-      <c r="H25" s="67"/>
-      <c r="I25" s="69">
+      <c r="G25" s="73">
+        <v>8136.1232879999998</v>
+      </c>
+      <c r="H25" s="66"/>
+      <c r="I25" s="68">
         <f t="shared" ref="I25" si="9">G25</f>
-        <v>9619.9999999999982</v>
-      </c>
-      <c r="J25" s="67"/>
-      <c r="K25" s="67">
+        <v>8136.1232879999998</v>
+      </c>
+      <c r="J25" s="66"/>
+      <c r="K25" s="66">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="L25" s="67"/>
-      <c r="M25" s="66">
+      <c r="L25" s="66"/>
+      <c r="M25" s="65">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N25" s="66">
+      <c r="N25" s="65">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="O25" s="67">
+      <c r="O25" s="66">
         <f t="shared" si="5"/>
-        <v>8136.1232879999998</v>
-      </c>
-      <c r="P25" s="67">
+        <v>10835.315690000001</v>
+      </c>
+      <c r="P25" s="66">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q25" s="67">
+      <c r="Q25" s="66">
         <f>'Calculo Servicios  (2)'!H23</f>
         <v>0</v>
       </c>
-      <c r="R25" s="66">
+      <c r="R25" s="65">
         <f t="shared" si="3"/>
-        <v>8136.1232879999998</v>
-      </c>
-      <c r="U25" s="96" t="s">
+        <v>10835.315690000001</v>
+      </c>
+      <c r="U25" s="95" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="163"/>
-      <c r="B26" s="160"/>
-      <c r="C26" s="97" t="s">
+      <c r="A26" s="162"/>
+      <c r="B26" s="159"/>
+      <c r="C26" s="96" t="s">
         <v>96</v>
       </c>
-      <c r="D26" s="169" t="str">
+      <c r="D26" s="168" t="str">
         <f>D18</f>
         <v>Lopez Gabriela</v>
       </c>
-      <c r="E26" s="166" t="s">
-        <v>148</v>
-      </c>
-      <c r="F26" s="167">
+      <c r="E26" s="165" t="s">
+        <v>147</v>
+      </c>
+      <c r="F26" s="166">
         <v>0.74</v>
       </c>
-      <c r="G26" s="69">
-        <v>40565.32</v>
-      </c>
-      <c r="H26" s="162">
-        <v>0</v>
-      </c>
-      <c r="I26" s="69">
-        <f>G26</f>
-        <v>40565.32</v>
-      </c>
-      <c r="J26" s="162" t="e">
+      <c r="G26" s="68">
+        <v>8136.1232879999998</v>
+      </c>
+      <c r="H26" s="161">
+        <v>0</v>
+      </c>
+      <c r="I26" s="68"/>
+      <c r="J26" s="161" t="e">
         <f>C8*F26/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K26" s="162">
+      <c r="K26" s="161">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L26" s="162"/>
-      <c r="M26" s="168">
+        <v>8136.1232879999998</v>
+      </c>
+      <c r="L26" s="161"/>
+      <c r="M26" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="N26" s="168">
+        <v>244.08369863999999</v>
+      </c>
+      <c r="N26" s="167">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O26" s="162">
+        <v>8380.2069866399997</v>
+      </c>
+      <c r="O26" s="161">
         <f t="shared" si="5"/>
-        <v>8136.1232879999998</v>
-      </c>
-      <c r="P26" s="162">
+        <v>10835.315690000001</v>
+      </c>
+      <c r="P26" s="161">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q26" s="162">
+      <c r="Q26" s="161">
         <f>'Calculo Servicios  (2)'!H24</f>
         <v>0</v>
       </c>
-      <c r="R26" s="168">
+      <c r="R26" s="167">
         <f t="shared" si="3"/>
-        <v>8136.1232879999998</v>
-      </c>
-      <c r="U26" s="96" t="s">
+        <v>19215.522676640001</v>
+      </c>
+      <c r="U26" s="95" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="113"/>
-      <c r="B27" s="73"/>
-      <c r="C27" s="96" t="s">
+      <c r="A27" s="112"/>
+      <c r="B27" s="72"/>
+      <c r="C27" s="95" t="s">
         <v>97</v>
       </c>
-      <c r="D27" s="115" t="str">
+      <c r="D27" s="114" t="str">
         <f>D15</f>
         <v>Cecilia Mariel Cassettari</v>
       </c>
-      <c r="E27" s="115"/>
-      <c r="F27" s="98">
+      <c r="E27" s="114"/>
+      <c r="F27" s="97">
         <v>0.74</v>
       </c>
-      <c r="G27" s="74">
-        <v>9619.9999999999982</v>
-      </c>
-      <c r="H27" s="67">
-        <v>0</v>
-      </c>
-      <c r="I27" s="69">
+      <c r="G27" s="73">
+        <v>8136.1232879999998</v>
+      </c>
+      <c r="H27" s="66">
+        <v>0</v>
+      </c>
+      <c r="I27" s="68">
         <f>G27</f>
-        <v>9619.9999999999982</v>
-      </c>
-      <c r="J27" s="67" t="e">
+        <v>8136.1232879999998</v>
+      </c>
+      <c r="J27" s="66" t="e">
         <f>C8*F27/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K27" s="67">
+      <c r="K27" s="66">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="L27" s="67"/>
-      <c r="M27" s="66">
+      <c r="L27" s="66"/>
+      <c r="M27" s="65">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N27" s="66">
+      <c r="N27" s="65">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="O27" s="67">
+      <c r="O27" s="66">
         <f t="shared" si="5"/>
-        <v>8136.1232879999998</v>
-      </c>
-      <c r="P27" s="67">
+        <v>10835.315690000001</v>
+      </c>
+      <c r="P27" s="66">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q27" s="67">
+      <c r="Q27" s="66">
         <f>'Calculo Servicios  (2)'!H25</f>
         <v>0</v>
       </c>
-      <c r="R27" s="66">
+      <c r="R27" s="65">
         <f t="shared" si="3"/>
-        <v>8136.1232879999998</v>
-      </c>
-      <c r="U27" s="96" t="s">
+        <v>10835.315690000001</v>
+      </c>
+      <c r="U27" s="95" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="28" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="176"/>
-      <c r="B28" s="177"/>
-      <c r="C28" s="178" t="s">
+      <c r="A28" s="233"/>
+      <c r="B28" s="234"/>
+      <c r="C28" s="96" t="s">
         <v>98</v>
       </c>
-      <c r="D28" s="179" t="str">
+      <c r="D28" s="168" t="str">
         <f>D16</f>
-        <v>Grandinetti Leonardo Alberto</v>
-      </c>
-      <c r="E28" s="180"/>
-      <c r="F28" s="181">
+        <v>Perez Sebastian</v>
+      </c>
+      <c r="E28" s="165"/>
+      <c r="F28" s="235">
         <v>0.74</v>
       </c>
-      <c r="G28" s="182">
-        <v>54169.696656614957</v>
-      </c>
-      <c r="H28" s="183">
-        <v>0</v>
-      </c>
-      <c r="I28" s="182"/>
-      <c r="J28" s="183">
-        <v>0</v>
-      </c>
-      <c r="K28" s="183">
+      <c r="G28" s="68">
+        <v>63930.91084431341</v>
+      </c>
+      <c r="H28" s="68">
+        <v>0</v>
+      </c>
+      <c r="I28" s="68">
+        <f>G28</f>
+        <v>63930.91084431341</v>
+      </c>
+      <c r="J28" s="68">
+        <v>0</v>
+      </c>
+      <c r="K28" s="68">
         <f t="shared" si="7"/>
-        <v>54169.696656614957</v>
-      </c>
-      <c r="L28" s="183"/>
-      <c r="M28" s="184">
+        <v>0</v>
+      </c>
+      <c r="L28" s="68"/>
+      <c r="M28" s="182">
         <f t="shared" si="4"/>
-        <v>1625.0908996984485</v>
-      </c>
-      <c r="N28" s="184">
+        <v>0</v>
+      </c>
+      <c r="N28" s="182">
         <f t="shared" si="8"/>
-        <v>55794.787556313408</v>
-      </c>
-      <c r="O28" s="183">
+        <v>0</v>
+      </c>
+      <c r="O28" s="68">
         <f t="shared" si="5"/>
-        <v>8136.1232879999998</v>
-      </c>
-      <c r="P28" s="183">
+        <v>10835.315690000001</v>
+      </c>
+      <c r="P28" s="68">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q28" s="183">
+      <c r="Q28" s="68">
         <f>'Calculo Servicios  (2)'!H26</f>
         <v>0</v>
       </c>
-      <c r="R28" s="184">
+      <c r="R28" s="182">
         <f t="shared" si="3"/>
-        <v>63930.91084431341</v>
-      </c>
-      <c r="U28" s="96" t="s">
+        <v>10835.315690000001</v>
+      </c>
+      <c r="U28" s="95" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:21" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="163"/>
-      <c r="B29" s="177"/>
-      <c r="C29" s="97" t="s">
+      <c r="A29" s="162"/>
+      <c r="B29" s="175"/>
+      <c r="C29" s="96" t="s">
         <v>99</v>
       </c>
-      <c r="D29" s="169" t="str">
+      <c r="D29" s="168" t="str">
         <f>D22</f>
         <v>Rodriguez Flavio/Rodriguez Mauro</v>
       </c>
-      <c r="E29" s="166" t="s">
-        <v>156</v>
-      </c>
-      <c r="F29" s="197">
+      <c r="E29" s="165" t="s">
+        <v>154</v>
+      </c>
+      <c r="F29" s="185">
         <v>0.74</v>
       </c>
-      <c r="G29" s="69">
-        <v>54169.696656614957</v>
-      </c>
-      <c r="H29" s="162">
-        <v>0</v>
-      </c>
-      <c r="I29" s="69">
+      <c r="G29" s="68">
+        <v>8136.1232879999998</v>
+      </c>
+      <c r="H29" s="161">
+        <v>0</v>
+      </c>
+      <c r="I29" s="68">
         <f>G29</f>
-        <v>54169.696656614957</v>
-      </c>
-      <c r="J29" s="162" t="e">
+        <v>8136.1232879999998</v>
+      </c>
+      <c r="J29" s="161" t="e">
         <f>C8*F29/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K29" s="162">
+      <c r="K29" s="161">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="L29" s="162"/>
-      <c r="M29" s="168">
+      <c r="L29" s="161"/>
+      <c r="M29" s="167">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N29" s="168">
+      <c r="N29" s="167">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="O29" s="162">
+      <c r="O29" s="161">
         <f t="shared" si="5"/>
-        <v>8136.1232879999998</v>
-      </c>
-      <c r="P29" s="162">
+        <v>10835.315690000001</v>
+      </c>
+      <c r="P29" s="161">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q29" s="162">
+      <c r="Q29" s="161">
         <f>'Calculo Servicios  (2)'!H27</f>
         <v>0</v>
       </c>
-      <c r="R29" s="168">
+      <c r="R29" s="167">
         <f t="shared" si="3"/>
-        <v>8136.1232879999998</v>
-      </c>
-      <c r="U29" s="97" t="s">
+        <v>10835.315690000001</v>
+      </c>
+      <c r="U29" s="96" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="30" spans="1:21" ht="21" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="75"/>
-      <c r="B30" s="73"/>
-      <c r="C30" s="72"/>
-      <c r="D30" s="72"/>
-      <c r="E30" s="72"/>
-      <c r="F30" s="71"/>
-      <c r="G30" s="70"/>
-      <c r="H30" s="67">
-        <v>0</v>
-      </c>
-      <c r="I30" s="69"/>
-      <c r="J30" s="68"/>
-      <c r="K30" s="67"/>
-      <c r="L30" s="68"/>
-      <c r="M30" s="66"/>
-      <c r="N30" s="66"/>
-      <c r="O30" s="67"/>
-      <c r="P30" s="67">
+      <c r="A30" s="74"/>
+      <c r="B30" s="72"/>
+      <c r="C30" s="71"/>
+      <c r="D30" s="71"/>
+      <c r="E30" s="71"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="69"/>
+      <c r="H30" s="66">
+        <v>0</v>
+      </c>
+      <c r="I30" s="68"/>
+      <c r="J30" s="67"/>
+      <c r="K30" s="66"/>
+      <c r="L30" s="67"/>
+      <c r="M30" s="65"/>
+      <c r="N30" s="65"/>
+      <c r="O30" s="66"/>
+      <c r="P30" s="66">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q30" s="67"/>
-      <c r="R30" s="111"/>
-      <c r="U30" s="96" t="s">
+      <c r="Q30" s="66"/>
+      <c r="R30" s="110"/>
+      <c r="U30" s="95" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="31" spans="1:21" s="60" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="234"/>
-      <c r="B31" s="235"/>
-      <c r="C31" s="235"/>
-      <c r="D31" s="65"/>
-      <c r="E31" s="65"/>
-      <c r="F31" s="99"/>
-      <c r="G31" s="63">
+    <row r="31" spans="1:21" s="59" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="221"/>
+      <c r="B31" s="222"/>
+      <c r="C31" s="222"/>
+      <c r="D31" s="64"/>
+      <c r="E31" s="64"/>
+      <c r="F31" s="98"/>
+      <c r="G31" s="62">
         <f>SUM(G11:G30)</f>
-        <v>4018054.8986706845</v>
-      </c>
-      <c r="H31" s="63">
+        <v>3130164.1365016159</v>
+      </c>
+      <c r="H31" s="62">
         <f>SUM(H11:H30)</f>
         <v>0</v>
       </c>
-      <c r="I31" s="64">
+      <c r="I31" s="63">
         <f>SUM(I11:I30)</f>
-        <v>2414480.2154854122</v>
-      </c>
-      <c r="J31" s="63"/>
-      <c r="K31" s="64">
+        <v>2672781.3927473403</v>
+      </c>
+      <c r="J31" s="62"/>
+      <c r="K31" s="63">
         <f>SUM(K11:K30)</f>
-        <v>1603574.6831852729</v>
-      </c>
-      <c r="L31" s="63"/>
-      <c r="M31" s="62"/>
-      <c r="N31" s="61"/>
-      <c r="O31" s="64">
+        <v>457382.74375427479</v>
+      </c>
+      <c r="L31" s="62"/>
+      <c r="M31" s="61"/>
+      <c r="N31" s="60"/>
+      <c r="O31" s="63">
         <f>SUM(O11:O30)</f>
-        <v>1099256.2247760003</v>
-      </c>
-      <c r="P31" s="64">
+        <v>1463939.0036300013</v>
+      </c>
+      <c r="P31" s="63">
         <f t="shared" ref="P31" si="10">SUM(P11:P30)</f>
         <v>0</v>
       </c>
-      <c r="Q31" s="64">
+      <c r="Q31" s="63">
         <f>SUM(Q11:Q30)</f>
-        <v>379696.63824000006</v>
-      </c>
-      <c r="R31" s="112">
+        <v>340046.28227999998</v>
+      </c>
+      <c r="R31" s="111">
         <f>O31+N31+P31+Q31</f>
-        <v>1478952.8630160003</v>
-      </c>
-      <c r="U31" s="96" t="s">
+        <v>1803985.2859100013</v>
+      </c>
+      <c r="U31" s="95" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="32" spans="1:21" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="231" t="s">
+      <c r="B32" s="218" t="s">
         <v>19</v>
       </c>
-      <c r="C32" s="232"/>
-      <c r="D32" s="232"/>
-      <c r="E32" s="232"/>
-      <c r="F32" s="232"/>
-      <c r="G32" s="232"/>
-      <c r="H32" s="232"/>
-      <c r="I32" s="232"/>
-      <c r="J32" s="232"/>
-      <c r="K32" s="232"/>
-      <c r="L32" s="232"/>
-      <c r="M32" s="232"/>
-      <c r="N32" s="232"/>
-      <c r="O32" s="232"/>
-      <c r="P32" s="232"/>
-      <c r="Q32" s="232"/>
-      <c r="R32" s="233"/>
-      <c r="U32" s="96" t="s">
+      <c r="C32" s="219"/>
+      <c r="D32" s="219"/>
+      <c r="E32" s="219"/>
+      <c r="F32" s="219"/>
+      <c r="G32" s="219"/>
+      <c r="H32" s="219"/>
+      <c r="I32" s="219"/>
+      <c r="J32" s="219"/>
+      <c r="K32" s="219"/>
+      <c r="L32" s="219"/>
+      <c r="M32" s="219"/>
+      <c r="N32" s="219"/>
+      <c r="O32" s="219"/>
+      <c r="P32" s="219"/>
+      <c r="Q32" s="219"/>
+      <c r="R32" s="220"/>
+      <c r="U32" s="95" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="33" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="F33" s="59"/>
-      <c r="G33" s="58"/>
-      <c r="H33" s="58"/>
-      <c r="I33" s="58"/>
-      <c r="J33" s="58"/>
-      <c r="K33" s="58" t="s">
+      <c r="F33" s="58"/>
+      <c r="G33" s="57"/>
+      <c r="H33" s="57"/>
+      <c r="I33" s="57"/>
+      <c r="J33" s="57"/>
+      <c r="K33" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="L33" s="58"/>
-      <c r="U33" s="96" t="s">
+      <c r="L33" s="57"/>
+      <c r="U33" s="95" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="34" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C34" s="225" t="s">
-        <v>154</v>
-      </c>
-      <c r="D34" s="225"/>
-      <c r="E34" s="225"/>
-      <c r="F34" s="225"/>
-      <c r="G34" s="225"/>
-      <c r="H34" s="225"/>
-      <c r="I34" s="225"/>
-      <c r="J34" s="225"/>
-      <c r="K34" s="225"/>
-      <c r="L34" s="225"/>
-      <c r="M34" s="225"/>
-      <c r="N34" s="225"/>
-      <c r="O34" s="225"/>
+      <c r="C34" s="236"/>
+      <c r="D34" s="236"/>
+      <c r="E34" s="236"/>
+      <c r="F34" s="236"/>
+      <c r="G34" s="236"/>
+      <c r="H34" s="236"/>
+      <c r="I34" s="236"/>
+      <c r="J34" s="236"/>
+      <c r="K34" s="236"/>
+      <c r="L34" s="236"/>
+      <c r="M34" s="236"/>
+      <c r="N34" s="236"/>
+      <c r="O34" s="236"/>
     </row>
     <row r="35" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C35" s="225"/>
-      <c r="D35" s="225"/>
-      <c r="E35" s="225"/>
-      <c r="F35" s="225"/>
-      <c r="G35" s="225"/>
-      <c r="H35" s="225"/>
-      <c r="I35" s="225"/>
-      <c r="J35" s="225"/>
-      <c r="K35" s="225"/>
-      <c r="L35" s="225"/>
-      <c r="M35" s="225"/>
-      <c r="N35" s="225"/>
-      <c r="O35" s="225"/>
+      <c r="C35" s="236"/>
+      <c r="D35" s="236"/>
+      <c r="E35" s="236"/>
+      <c r="F35" s="236"/>
+      <c r="G35" s="236"/>
+      <c r="H35" s="236"/>
+      <c r="I35" s="236"/>
+      <c r="J35" s="236"/>
+      <c r="K35" s="236"/>
+      <c r="L35" s="236"/>
+      <c r="M35" s="236"/>
+      <c r="N35" s="236"/>
+      <c r="O35" s="236"/>
     </row>
     <row r="36" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C36" s="225"/>
-      <c r="D36" s="225"/>
-      <c r="E36" s="225"/>
-      <c r="F36" s="225"/>
-      <c r="G36" s="225"/>
-      <c r="H36" s="225"/>
-      <c r="I36" s="225"/>
-      <c r="J36" s="225"/>
-      <c r="K36" s="225"/>
-      <c r="L36" s="225"/>
-      <c r="M36" s="225"/>
-      <c r="N36" s="225"/>
-      <c r="O36" s="225"/>
+      <c r="C36" s="236"/>
+      <c r="D36" s="236"/>
+      <c r="E36" s="236"/>
+      <c r="F36" s="236"/>
+      <c r="G36" s="236"/>
+      <c r="H36" s="236"/>
+      <c r="I36" s="236"/>
+      <c r="J36" s="236"/>
+      <c r="K36" s="236"/>
+      <c r="L36" s="236"/>
+      <c r="M36" s="236"/>
+      <c r="N36" s="236"/>
+      <c r="O36" s="236"/>
     </row>
     <row r="37" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C37" s="225"/>
-      <c r="D37" s="225"/>
-      <c r="E37" s="225"/>
-      <c r="F37" s="225"/>
-      <c r="G37" s="225"/>
-      <c r="H37" s="225"/>
-      <c r="I37" s="225"/>
-      <c r="J37" s="225"/>
-      <c r="K37" s="225"/>
-      <c r="L37" s="225"/>
-      <c r="M37" s="225"/>
-      <c r="N37" s="225"/>
-      <c r="O37" s="225"/>
+      <c r="C37" s="236"/>
+      <c r="D37" s="236"/>
+      <c r="E37" s="236"/>
+      <c r="F37" s="236"/>
+      <c r="G37" s="236"/>
+      <c r="H37" s="236"/>
+      <c r="I37" s="236"/>
+      <c r="J37" s="236"/>
+      <c r="K37" s="236"/>
+      <c r="L37" s="236"/>
+      <c r="M37" s="236"/>
+      <c r="N37" s="236"/>
+      <c r="O37" s="236"/>
     </row>
     <row r="38" spans="3:21" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="225"/>
-      <c r="D38" s="225"/>
-      <c r="E38" s="225"/>
-      <c r="F38" s="225"/>
-      <c r="G38" s="225"/>
-      <c r="H38" s="225"/>
-      <c r="I38" s="225"/>
-      <c r="J38" s="225"/>
-      <c r="K38" s="225"/>
-      <c r="L38" s="225"/>
-      <c r="M38" s="225"/>
-      <c r="N38" s="225"/>
-      <c r="O38" s="225"/>
+      <c r="C38" s="236"/>
+      <c r="D38" s="236"/>
+      <c r="E38" s="236"/>
+      <c r="F38" s="236"/>
+      <c r="G38" s="236"/>
+      <c r="H38" s="236"/>
+      <c r="I38" s="236"/>
+      <c r="J38" s="236"/>
+      <c r="K38" s="236"/>
+      <c r="L38" s="236"/>
+      <c r="M38" s="236"/>
+      <c r="N38" s="236"/>
+      <c r="O38" s="236"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -4493,7 +4450,7 @@
     <mergeCell ref="C5:D5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="72" fitToWidth="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup scale="69" fitToWidth="0" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -4503,1007 +4460,1007 @@
   <dimension ref="A1:O47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.140625" style="117" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" style="117" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" style="117" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" style="117" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" style="117" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.42578125" style="117" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14" style="117" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="11.42578125" style="117"/>
-    <col min="13" max="13" width="14.7109375" style="117" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.5703125" style="117" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="11.42578125" style="117"/>
+    <col min="1" max="1" width="12.140625" style="116" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" style="116" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" style="116" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" style="116" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" style="116" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.42578125" style="116" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14" style="116" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="11.42578125" style="116"/>
+    <col min="13" max="13" width="14.7109375" style="116" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.5703125" style="116" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="11.42578125" style="116"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A1" s="237" t="s">
+      <c r="A1" s="224" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="238"/>
-      <c r="C1" s="238"/>
-      <c r="D1" s="238"/>
-      <c r="E1" s="239"/>
+      <c r="B1" s="225"/>
+      <c r="C1" s="225"/>
+      <c r="D1" s="225"/>
+      <c r="E1" s="226"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A2" s="158"/>
-      <c r="B2" s="143"/>
-      <c r="C2" s="143"/>
-      <c r="D2" s="157" t="s">
+      <c r="A2" s="157"/>
+      <c r="B2" s="142"/>
+      <c r="C2" s="142"/>
+      <c r="D2" s="156" t="s">
         <v>79</v>
       </c>
-      <c r="E2" s="154"/>
+      <c r="E2" s="153"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A3" s="156">
+      <c r="A3" s="155">
         <f>13+28+19</f>
         <v>60</v>
       </c>
-      <c r="B3" s="110">
+      <c r="B3" s="109">
         <v>10531.71</v>
       </c>
-      <c r="C3" s="155">
+      <c r="C3" s="154">
         <f>+B3/A3</f>
         <v>175.52849999999998</v>
       </c>
-      <c r="D3" s="155">
+      <c r="D3" s="154">
         <v>4863.8999999999996</v>
       </c>
-      <c r="E3" s="154" t="s">
-        <v>141</v>
-      </c>
-      <c r="I3" s="117" t="s">
+      <c r="E3" s="153" t="s">
+        <v>140</v>
+      </c>
+      <c r="I3" s="116" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="153"/>
-      <c r="B4" s="152"/>
-      <c r="C4" s="152"/>
-      <c r="D4" s="152"/>
-      <c r="E4" s="151"/>
+      <c r="A4" s="152"/>
+      <c r="B4" s="151"/>
+      <c r="C4" s="151"/>
+      <c r="D4" s="151"/>
+      <c r="E4" s="150"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A5" s="150"/>
-      <c r="B5" s="150"/>
-      <c r="C5" s="150"/>
-      <c r="D5" s="150"/>
-      <c r="E5" s="150"/>
+      <c r="A5" s="149"/>
+      <c r="B5" s="149"/>
+      <c r="C5" s="149"/>
+      <c r="D5" s="149"/>
+      <c r="E5" s="149"/>
     </row>
     <row r="6" spans="1:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="150"/>
-      <c r="B6" s="150"/>
-      <c r="C6" s="150"/>
-      <c r="D6" s="150"/>
-      <c r="E6" s="150"/>
+      <c r="A6" s="149"/>
+      <c r="B6" s="149"/>
+      <c r="C6" s="149"/>
+      <c r="D6" s="149"/>
+      <c r="E6" s="149"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A7" s="240" t="s">
+      <c r="A7" s="227" t="s">
         <v>77</v>
       </c>
-      <c r="B7" s="241"/>
-      <c r="C7" s="241"/>
-      <c r="D7" s="241"/>
-      <c r="E7" s="241"/>
-      <c r="F7" s="241"/>
-      <c r="G7" s="241"/>
-      <c r="H7" s="242"/>
-      <c r="L7" s="117" t="s">
+      <c r="B7" s="228"/>
+      <c r="C7" s="228"/>
+      <c r="D7" s="228"/>
+      <c r="E7" s="228"/>
+      <c r="F7" s="228"/>
+      <c r="G7" s="228"/>
+      <c r="H7" s="229"/>
+      <c r="L7" s="116" t="s">
         <v>72</v>
       </c>
-      <c r="M7" s="117" t="s">
+      <c r="M7" s="116" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A8" s="109">
+      <c r="A8" s="108">
         <v>400523.88</v>
       </c>
-      <c r="B8" s="148" t="s">
+      <c r="B8" s="147" t="s">
         <v>75</v>
       </c>
-      <c r="C8" s="148" t="s">
+      <c r="C8" s="147" t="s">
         <v>74</v>
       </c>
-      <c r="D8" s="148" t="s">
+      <c r="D8" s="147" t="s">
         <v>73</v>
       </c>
-      <c r="E8" s="149">
+      <c r="E8" s="148">
         <f>3935/2</f>
         <v>1967.5</v>
       </c>
-      <c r="F8" s="148" t="s">
+      <c r="F8" s="147" t="s">
         <v>72</v>
       </c>
-      <c r="G8" s="148" t="s">
+      <c r="G8" s="147" t="s">
         <v>71</v>
       </c>
-      <c r="H8" s="147" t="s">
+      <c r="H8" s="146" t="s">
         <v>70</v>
       </c>
-      <c r="K8" s="143">
+      <c r="K8" s="142">
         <v>19</v>
       </c>
-      <c r="L8" s="129">
+      <c r="L8" s="128">
         <v>7502.93</v>
       </c>
-      <c r="M8" s="129">
+      <c r="M8" s="128">
         <v>2365.2600000000002</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A9" s="146" t="s">
+      <c r="A9" s="145" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="143">
+      <c r="B9" s="142">
         <v>1617</v>
       </c>
-      <c r="C9" s="143">
+      <c r="C9" s="142">
         <f>B9+J25</f>
         <v>1689</v>
       </c>
-      <c r="D9" s="143">
+      <c r="D9" s="142">
         <f t="shared" ref="D9:D20" si="0">+C9-B9</f>
         <v>72</v>
       </c>
-      <c r="E9" s="106">
+      <c r="E9" s="105">
         <f>+D9/E8</f>
         <v>3.6594663278271919E-2</v>
       </c>
-      <c r="F9" s="105">
+      <c r="F9" s="104">
         <f>+A8*E9</f>
         <v>14657.036523506989</v>
       </c>
-      <c r="G9" s="105">
+      <c r="G9" s="104">
         <f>+(A8*A23)/12</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H9" s="104">
+      <c r="H9" s="103">
         <f>+G9+F9</f>
         <v>24606.517913595933</v>
       </c>
-      <c r="K9" s="117">
+      <c r="K9" s="116">
         <v>106</v>
       </c>
-      <c r="L9" s="129">
+      <c r="L9" s="128">
         <f>+L8*O9</f>
         <v>1575.6152999999999</v>
       </c>
-      <c r="M9" s="117">
+      <c r="M9" s="116">
         <f>M8*21%</f>
         <v>496.70460000000003</v>
       </c>
-      <c r="N9" s="117" t="s">
+      <c r="N9" s="116" t="s">
         <v>69</v>
       </c>
-      <c r="O9" s="108">
+      <c r="O9" s="107">
         <v>0.21</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A10" s="144" t="s">
+      <c r="A10" s="143" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="143">
+      <c r="B10" s="142">
         <v>4104</v>
       </c>
-      <c r="C10" s="143">
+      <c r="C10" s="142">
         <f t="shared" ref="C10:C20" si="1">B10+J26</f>
         <v>4195</v>
       </c>
-      <c r="D10" s="143">
+      <c r="D10" s="142">
         <f t="shared" si="0"/>
         <v>91</v>
       </c>
-      <c r="E10" s="106">
+      <c r="E10" s="105">
         <f>+D10/E8</f>
         <v>4.6251588310038116E-2</v>
       </c>
-      <c r="F10" s="105">
+      <c r="F10" s="104">
         <f>+A8*E10</f>
         <v>18524.865606099109</v>
       </c>
-      <c r="G10" s="105">
+      <c r="G10" s="104">
         <f>+G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H10" s="104">
+      <c r="H10" s="103">
         <f>+G10+F10</f>
         <v>28474.346996188055</v>
       </c>
-      <c r="K10" s="117">
+      <c r="K10" s="116">
         <v>60</v>
       </c>
-      <c r="L10" s="129">
+      <c r="L10" s="128">
         <f>+L8*O10</f>
         <v>481.98822320000005</v>
       </c>
-      <c r="M10" s="117">
+      <c r="M10" s="116">
         <f>+M8*6.424%</f>
         <v>151.94430240000003</v>
       </c>
-      <c r="N10" s="117" t="s">
+      <c r="N10" s="116" t="s">
         <v>68</v>
       </c>
-      <c r="O10" s="107">
+      <c r="O10" s="106">
         <v>6.4240000000000005E-2</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A11" s="144" t="s">
+      <c r="A11" s="143" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="143">
+      <c r="B11" s="142">
         <v>7644</v>
       </c>
-      <c r="C11" s="143">
+      <c r="C11" s="142">
         <f t="shared" si="1"/>
         <v>7807</v>
       </c>
-      <c r="D11" s="143">
+      <c r="D11" s="142">
         <f t="shared" si="0"/>
         <v>163</v>
       </c>
-      <c r="E11" s="106">
+      <c r="E11" s="105">
         <f>+D11/E8</f>
         <v>8.2846251588310035E-2</v>
       </c>
-      <c r="F11" s="105">
+      <c r="F11" s="104">
         <f>+A8*E11</f>
         <v>33181.902129606096</v>
       </c>
-      <c r="G11" s="105">
+      <c r="G11" s="104">
         <f>G10</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H11" s="104">
+      <c r="H11" s="103">
         <f>+G11+F11</f>
         <v>43131.383519695039</v>
       </c>
-      <c r="K11" s="117">
+      <c r="K11" s="116">
         <v>79</v>
       </c>
-      <c r="L11" s="129">
+      <c r="L11" s="128">
         <f>+L8*0.001%</f>
         <v>7.5029300000000007E-2</v>
       </c>
-      <c r="M11" s="117">
+      <c r="M11" s="116">
         <v>0.03</v>
       </c>
-      <c r="N11" s="117" t="s">
+      <c r="N11" s="116" t="s">
         <v>67</v>
       </c>
-      <c r="O11" s="129">
+      <c r="O11" s="128">
         <v>0.1</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A12" s="144" t="s">
+      <c r="A12" s="143" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="143">
+      <c r="B12" s="142">
         <v>6554</v>
       </c>
-      <c r="C12" s="143">
+      <c r="C12" s="142">
         <f t="shared" si="1"/>
         <v>6730</v>
       </c>
-      <c r="D12" s="143">
+      <c r="D12" s="142">
         <f t="shared" si="0"/>
         <v>176</v>
       </c>
-      <c r="E12" s="106">
+      <c r="E12" s="105">
         <f>+D12/E8</f>
         <v>8.9453621346886919E-2</v>
       </c>
-      <c r="F12" s="105">
+      <c r="F12" s="104">
         <f>+A8*E12</f>
         <v>35828.311501905977</v>
       </c>
-      <c r="G12" s="105">
+      <c r="G12" s="104">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H12" s="104">
+      <c r="H12" s="103">
         <f t="shared" ref="H12:H20" si="2">SUM(F12:G12)</f>
         <v>45777.792891994919</v>
       </c>
-      <c r="K12" s="117">
+      <c r="K12" s="116">
         <v>89</v>
       </c>
-      <c r="L12" s="129">
+      <c r="L12" s="128">
         <v>400</v>
       </c>
-      <c r="M12" s="117">
+      <c r="M12" s="116">
         <v>253</v>
       </c>
-      <c r="N12" s="117" t="s">
+      <c r="N12" s="116" t="s">
         <v>66</v>
       </c>
-      <c r="O12" s="117">
+      <c r="O12" s="116">
         <v>653</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A13" s="144" t="s">
+      <c r="A13" s="143" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="143">
+      <c r="B13" s="142">
         <v>7564</v>
       </c>
-      <c r="C13" s="143">
+      <c r="C13" s="142">
         <f t="shared" si="1"/>
         <v>7767</v>
       </c>
-      <c r="D13" s="143">
+      <c r="D13" s="142">
         <f t="shared" si="0"/>
         <v>203</v>
       </c>
-      <c r="E13" s="106">
+      <c r="E13" s="105">
         <f>+D13/E8</f>
         <v>0.10317662007623889</v>
       </c>
-      <c r="F13" s="105">
+      <c r="F13" s="104">
         <f>+A8*E13</f>
         <v>41324.700198221093</v>
       </c>
-      <c r="G13" s="105">
+      <c r="G13" s="104">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H13" s="104">
+      <c r="H13" s="103">
         <f t="shared" si="2"/>
         <v>51274.181588310035</v>
       </c>
-      <c r="K13" s="117">
+      <c r="K13" s="116">
         <v>140</v>
       </c>
-      <c r="L13" s="145">
+      <c r="L13" s="144">
         <f>SUM(L8:L12)-0.45</f>
         <v>9960.1585524999991</v>
       </c>
-      <c r="M13" s="117">
+      <c r="M13" s="116">
         <f>SUM(M8:M12)</f>
         <v>3266.9389024000006</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A14" s="144" t="s">
+      <c r="A14" s="143" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="143">
+      <c r="B14" s="142">
         <v>10119</v>
       </c>
-      <c r="C14" s="143">
+      <c r="C14" s="142">
         <f t="shared" si="1"/>
         <v>10334</v>
       </c>
-      <c r="D14" s="143">
+      <c r="D14" s="142">
         <f t="shared" si="0"/>
         <v>215</v>
       </c>
-      <c r="E14" s="106">
+      <c r="E14" s="105">
         <f>+D14/E8</f>
         <v>0.10927573062261753</v>
       </c>
-      <c r="F14" s="105">
+      <c r="F14" s="104">
         <f>+A8*E14</f>
         <v>43767.539618805589</v>
       </c>
-      <c r="G14" s="105">
+      <c r="G14" s="104">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H14" s="104">
+      <c r="H14" s="103">
         <f t="shared" si="2"/>
         <v>53717.021008894531</v>
       </c>
-      <c r="K14" s="117">
+      <c r="K14" s="116">
         <v>143</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A15" s="144" t="s">
+      <c r="A15" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="143">
+      <c r="B15" s="142">
         <v>8986</v>
       </c>
-      <c r="C15" s="143">
+      <c r="C15" s="142">
         <f t="shared" si="1"/>
         <v>9068</v>
       </c>
-      <c r="D15" s="143">
+      <c r="D15" s="142">
         <f t="shared" si="0"/>
         <v>82</v>
       </c>
-      <c r="E15" s="106">
+      <c r="E15" s="105">
         <f>+D15/E8</f>
         <v>4.1677255400254132E-2</v>
       </c>
-      <c r="F15" s="105">
+      <c r="F15" s="104">
         <f>+A8*E15</f>
         <v>16692.736040660737</v>
       </c>
-      <c r="G15" s="105">
+      <c r="G15" s="104">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H15" s="104">
+      <c r="H15" s="103">
         <f t="shared" si="2"/>
         <v>26642.217430749683</v>
       </c>
-      <c r="K15" s="117">
+      <c r="K15" s="116">
         <v>221</v>
       </c>
-      <c r="L15" s="117">
+      <c r="L15" s="116">
         <f>+L13+M13</f>
         <v>13227.0974549</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A16" s="144" t="s">
+      <c r="A16" s="143" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="143">
+      <c r="B16" s="142">
         <v>7032</v>
       </c>
-      <c r="C16" s="143">
+      <c r="C16" s="142">
         <f t="shared" si="1"/>
         <v>7034</v>
       </c>
-      <c r="D16" s="143">
+      <c r="D16" s="142">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="E16" s="106">
+      <c r="E16" s="105">
         <f>+D16/E8</f>
         <v>1.0165184243964421E-3</v>
       </c>
-      <c r="F16" s="105">
+      <c r="F16" s="104">
         <f>+A8*E16</f>
         <v>407.13990343074965</v>
       </c>
-      <c r="G16" s="105">
+      <c r="G16" s="104">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H16" s="104">
+      <c r="H16" s="103">
         <f t="shared" si="2"/>
         <v>10356.621293519693</v>
       </c>
-      <c r="K16" s="117">
+      <c r="K16" s="116">
         <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="A17" s="144" t="s">
+      <c r="A17" s="143" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="143">
+      <c r="B17" s="142">
         <v>1623</v>
       </c>
-      <c r="C17" s="143">
+      <c r="C17" s="142">
         <f t="shared" si="1"/>
         <v>1668</v>
       </c>
-      <c r="D17" s="143">
+      <c r="D17" s="142">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="E17" s="106">
+      <c r="E17" s="105">
         <f>+D17/E8</f>
         <v>2.2871664548919948E-2</v>
       </c>
-      <c r="F17" s="105">
+      <c r="F17" s="104">
         <f>+A8*E17</f>
         <v>9160.6478271918677</v>
       </c>
-      <c r="G17" s="105">
+      <c r="G17" s="104">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H17" s="104">
+      <c r="H17" s="103">
         <f t="shared" si="2"/>
         <v>19110.12921728081</v>
       </c>
-      <c r="K17" s="117">
+      <c r="K17" s="116">
         <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="A18" s="144" t="s">
+      <c r="A18" s="143" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="143">
+      <c r="B18" s="142">
         <v>3932</v>
       </c>
-      <c r="C18" s="143">
+      <c r="C18" s="142">
         <f t="shared" si="1"/>
         <v>4021</v>
       </c>
-      <c r="D18" s="143">
+      <c r="D18" s="142">
         <f t="shared" si="0"/>
         <v>89</v>
       </c>
-      <c r="E18" s="106">
+      <c r="E18" s="105">
         <f>+D18/E8</f>
         <v>4.5235069885641674E-2</v>
       </c>
-      <c r="F18" s="105">
+      <c r="F18" s="104">
         <f>+A8*E18</f>
         <v>18117.725702668358</v>
       </c>
-      <c r="G18" s="105">
+      <c r="G18" s="104">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H18" s="104">
+      <c r="H18" s="103">
         <f t="shared" si="2"/>
         <v>28067.2070927573</v>
       </c>
-      <c r="K18" s="117">
+      <c r="K18" s="116">
         <v>113</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="A19" s="144" t="s">
+      <c r="A19" s="143" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="143">
+      <c r="B19" s="142">
         <v>6887</v>
       </c>
-      <c r="C19" s="143">
+      <c r="C19" s="142">
         <f t="shared" si="1"/>
         <v>6994</v>
       </c>
-      <c r="D19" s="143">
+      <c r="D19" s="142">
         <f t="shared" si="0"/>
         <v>107</v>
       </c>
-      <c r="E19" s="106">
+      <c r="E19" s="105">
         <f>+D19/E8</f>
         <v>5.4383735705209657E-2</v>
       </c>
-      <c r="F19" s="105">
+      <c r="F19" s="104">
         <f>+A8*E19</f>
         <v>21781.98483354511</v>
       </c>
-      <c r="G19" s="105">
+      <c r="G19" s="104">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H19" s="104">
+      <c r="H19" s="103">
         <f t="shared" si="2"/>
         <v>31731.466223634052</v>
       </c>
-      <c r="K19" s="117">
+      <c r="K19" s="116">
         <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="A20" s="144" t="s">
+      <c r="A20" s="143" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="143">
+      <c r="B20" s="142">
         <v>1884</v>
       </c>
-      <c r="C20" s="143">
+      <c r="C20" s="142">
         <f t="shared" si="1"/>
         <v>2020</v>
       </c>
-      <c r="D20" s="143">
+      <c r="D20" s="142">
         <f t="shared" si="0"/>
         <v>136</v>
       </c>
-      <c r="E20" s="106">
+      <c r="E20" s="105">
         <f>+D20/E8</f>
         <v>6.9123252858958067E-2</v>
       </c>
-      <c r="F20" s="105">
+      <c r="F20" s="104">
         <f>+A8*E20</f>
         <v>27685.513433290977</v>
       </c>
-      <c r="G20" s="105">
+      <c r="G20" s="104">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H20" s="104">
+      <c r="H20" s="103">
         <f t="shared" si="2"/>
         <v>37634.994823379922</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="142" t="s">
-        <v>140</v>
-      </c>
-      <c r="B21" s="141"/>
-      <c r="C21" s="141"/>
-      <c r="D21" s="140">
+      <c r="A21" s="141" t="s">
+        <v>139</v>
+      </c>
+      <c r="B21" s="140"/>
+      <c r="C21" s="140"/>
+      <c r="D21" s="139">
         <f>SUM(D9:D20)</f>
         <v>1381</v>
       </c>
-      <c r="E21" s="139"/>
-      <c r="F21" s="119"/>
-      <c r="G21" s="119"/>
-      <c r="H21" s="103">
+      <c r="E21" s="138"/>
+      <c r="F21" s="118"/>
+      <c r="G21" s="118"/>
+      <c r="H21" s="102">
         <f>SUM(H9:H20)</f>
         <v>400523.88</v>
       </c>
-      <c r="J21" s="129">
+      <c r="J21" s="128">
         <f>+H21-A8</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="102">
+      <c r="A22" s="101">
         <f>+D21/E8</f>
         <v>0.70190597204574334</v>
       </c>
-      <c r="B22" s="138" t="s">
+      <c r="B22" s="137" t="s">
         <v>65</v>
       </c>
-      <c r="L22" s="137"/>
+      <c r="L22" s="136"/>
     </row>
     <row r="23" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="101">
+      <c r="A23" s="100">
         <f>100%-A22</f>
         <v>0.29809402795425666</v>
       </c>
-      <c r="B23" s="136" t="s">
+      <c r="B23" s="135" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="135"/>
-      <c r="J25" s="117">
+      <c r="A25" s="134"/>
+      <c r="J25" s="116">
         <v>72</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="J26" s="117">
+      <c r="J26" s="116">
         <v>91</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="J27" s="117">
+      <c r="J27" s="116">
         <v>163</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B28" s="243" t="s">
-        <v>139</v>
-      </c>
-      <c r="C28" s="244"/>
-      <c r="D28" s="244"/>
-      <c r="E28" s="244"/>
-      <c r="F28" s="245"/>
-      <c r="J28" s="117">
+      <c r="B28" s="230" t="s">
+        <v>138</v>
+      </c>
+      <c r="C28" s="231"/>
+      <c r="D28" s="231"/>
+      <c r="E28" s="231"/>
+      <c r="F28" s="232"/>
+      <c r="J28" s="116">
         <v>176</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B29" s="134" t="s">
-        <v>138</v>
-      </c>
-      <c r="C29" s="133" t="s">
+      <c r="B29" s="133" t="s">
         <v>137</v>
       </c>
-      <c r="D29" s="133" t="s">
+      <c r="C29" s="132" t="s">
         <v>136</v>
       </c>
-      <c r="E29" s="133" t="s">
+      <c r="D29" s="132" t="s">
         <v>135</v>
       </c>
-      <c r="F29" s="132" t="s">
+      <c r="E29" s="132" t="s">
         <v>134</v>
       </c>
-      <c r="J29" s="117">
+      <c r="F29" s="131" t="s">
+        <v>133</v>
+      </c>
+      <c r="J29" s="116">
         <v>203</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B30" s="128" t="s">
-        <v>133</v>
-      </c>
-      <c r="C30" s="105">
+      <c r="B30" s="127" t="s">
+        <v>132</v>
+      </c>
+      <c r="C30" s="104">
         <v>4000</v>
       </c>
-      <c r="D30" s="105">
-        <v>0</v>
-      </c>
-      <c r="E30" s="126"/>
-      <c r="F30" s="104">
+      <c r="D30" s="104">
+        <v>0</v>
+      </c>
+      <c r="E30" s="125"/>
+      <c r="F30" s="103">
         <f>+C30</f>
         <v>4000</v>
       </c>
-      <c r="J30" s="131">
+      <c r="J30" s="130">
         <v>215</v>
       </c>
-      <c r="M30" s="117">
+      <c r="M30" s="116">
         <f>+H21-A8</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B31" s="128" t="s">
-        <v>132</v>
-      </c>
-      <c r="C31" s="105">
+      <c r="B31" s="127" t="s">
+        <v>131</v>
+      </c>
+      <c r="C31" s="104">
         <v>4000</v>
       </c>
-      <c r="D31" s="105">
-        <v>0</v>
-      </c>
-      <c r="E31" s="126"/>
-      <c r="F31" s="104">
+      <c r="D31" s="104">
+        <v>0</v>
+      </c>
+      <c r="E31" s="125"/>
+      <c r="F31" s="103">
         <f t="shared" ref="F31:F44" si="3">+F30+C31-D31</f>
         <v>8000</v>
       </c>
-      <c r="J31" s="117">
+      <c r="J31" s="116">
         <v>82</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B32" s="128" t="s">
-        <v>131</v>
-      </c>
-      <c r="C32" s="105">
+      <c r="B32" s="127" t="s">
+        <v>130</v>
+      </c>
+      <c r="C32" s="104">
         <v>4000</v>
       </c>
-      <c r="D32" s="105">
-        <v>0</v>
-      </c>
-      <c r="E32" s="126"/>
-      <c r="F32" s="104">
+      <c r="D32" s="104">
+        <v>0</v>
+      </c>
+      <c r="E32" s="125"/>
+      <c r="F32" s="103">
         <f t="shared" si="3"/>
         <v>12000</v>
       </c>
-      <c r="J32" s="117">
+      <c r="J32" s="116">
         <v>2</v>
       </c>
     </row>
     <row r="33" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B33" s="128" t="s">
-        <v>130</v>
-      </c>
-      <c r="C33" s="105">
+      <c r="B33" s="127" t="s">
+        <v>129</v>
+      </c>
+      <c r="C33" s="104">
         <v>4000</v>
       </c>
-      <c r="D33" s="105">
-        <v>0</v>
-      </c>
-      <c r="E33" s="126"/>
-      <c r="F33" s="104">
+      <c r="D33" s="104">
+        <v>0</v>
+      </c>
+      <c r="E33" s="125"/>
+      <c r="F33" s="103">
         <f t="shared" si="3"/>
         <v>16000</v>
       </c>
-      <c r="J33" s="117">
+      <c r="J33" s="116">
         <v>45</v>
       </c>
-      <c r="K33" s="130">
+      <c r="K33" s="129">
         <f>11934.02-11933.71</f>
         <v>0.31000000000130967</v>
       </c>
     </row>
     <row r="34" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B34" s="128" t="s">
-        <v>129</v>
-      </c>
-      <c r="C34" s="105">
+      <c r="B34" s="127" t="s">
+        <v>128</v>
+      </c>
+      <c r="C34" s="104">
         <v>4000</v>
       </c>
-      <c r="D34" s="105">
-        <v>0</v>
-      </c>
-      <c r="E34" s="126"/>
-      <c r="F34" s="104">
+      <c r="D34" s="104">
+        <v>0</v>
+      </c>
+      <c r="E34" s="125"/>
+      <c r="F34" s="103">
         <f t="shared" si="3"/>
         <v>20000</v>
       </c>
-      <c r="J34" s="117">
+      <c r="J34" s="116">
         <v>89</v>
       </c>
     </row>
     <row r="35" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B35" s="128" t="s">
-        <v>128</v>
-      </c>
-      <c r="C35" s="105">
+      <c r="B35" s="127" t="s">
+        <v>127</v>
+      </c>
+      <c r="C35" s="104">
         <v>4000</v>
       </c>
-      <c r="D35" s="105">
-        <v>0</v>
-      </c>
-      <c r="E35" s="126"/>
-      <c r="F35" s="104">
+      <c r="D35" s="104">
+        <v>0</v>
+      </c>
+      <c r="E35" s="125"/>
+      <c r="F35" s="103">
         <f t="shared" si="3"/>
         <v>24000</v>
       </c>
-      <c r="J35" s="117">
+      <c r="J35" s="116">
         <v>107</v>
       </c>
     </row>
     <row r="36" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B36" s="128" t="s">
-        <v>127</v>
-      </c>
-      <c r="C36" s="105">
+      <c r="B36" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="C36" s="104">
         <v>4000</v>
       </c>
-      <c r="D36" s="105">
-        <v>0</v>
-      </c>
-      <c r="E36" s="126"/>
-      <c r="F36" s="104">
+      <c r="D36" s="104">
+        <v>0</v>
+      </c>
+      <c r="E36" s="125"/>
+      <c r="F36" s="103">
         <f t="shared" si="3"/>
         <v>28000</v>
       </c>
-      <c r="J36" s="117">
+      <c r="J36" s="116">
         <v>136</v>
       </c>
     </row>
     <row r="37" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B37" s="128" t="s">
-        <v>126</v>
-      </c>
-      <c r="C37" s="127">
+      <c r="B37" s="127" t="s">
+        <v>125</v>
+      </c>
+      <c r="C37" s="126">
         <v>4000</v>
       </c>
-      <c r="D37" s="105">
-        <v>0</v>
-      </c>
-      <c r="E37" s="126"/>
-      <c r="F37" s="104">
+      <c r="D37" s="104">
+        <v>0</v>
+      </c>
+      <c r="E37" s="125"/>
+      <c r="F37" s="103">
         <f t="shared" si="3"/>
         <v>32000</v>
       </c>
     </row>
     <row r="38" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B38" s="128" t="s">
-        <v>125</v>
-      </c>
-      <c r="C38" s="127">
+      <c r="B38" s="127" t="s">
+        <v>124</v>
+      </c>
+      <c r="C38" s="126">
         <v>4000</v>
       </c>
-      <c r="D38" s="127">
+      <c r="D38" s="126">
         <v>3500</v>
       </c>
-      <c r="E38" s="126" t="s">
-        <v>124</v>
-      </c>
-      <c r="F38" s="104">
+      <c r="E38" s="125" t="s">
+        <v>123</v>
+      </c>
+      <c r="F38" s="103">
         <f t="shared" si="3"/>
         <v>32500</v>
       </c>
-      <c r="M38" s="129">
+      <c r="M38" s="128">
         <f>88.05-100</f>
         <v>-11.950000000000003</v>
       </c>
     </row>
     <row r="39" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B39" s="128" t="s">
-        <v>123</v>
-      </c>
-      <c r="C39" s="127">
+      <c r="B39" s="127" t="s">
+        <v>122</v>
+      </c>
+      <c r="C39" s="126">
         <v>4000</v>
       </c>
-      <c r="D39" s="126"/>
-      <c r="E39" s="126"/>
-      <c r="F39" s="104">
+      <c r="D39" s="125"/>
+      <c r="E39" s="125"/>
+      <c r="F39" s="103">
         <f t="shared" si="3"/>
         <v>36500</v>
       </c>
     </row>
     <row r="40" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B40" s="128" t="s">
-        <v>122</v>
-      </c>
-      <c r="C40" s="127">
+      <c r="B40" s="127" t="s">
+        <v>121</v>
+      </c>
+      <c r="C40" s="126">
         <v>4000</v>
       </c>
-      <c r="D40" s="126"/>
-      <c r="E40" s="126"/>
-      <c r="F40" s="104">
+      <c r="D40" s="125"/>
+      <c r="E40" s="125"/>
+      <c r="F40" s="103">
         <f t="shared" si="3"/>
         <v>40500</v>
       </c>
     </row>
     <row r="41" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B41" s="128" t="s">
-        <v>121</v>
-      </c>
-      <c r="C41" s="127">
+      <c r="B41" s="127" t="s">
+        <v>120</v>
+      </c>
+      <c r="C41" s="126">
         <v>4000</v>
       </c>
-      <c r="D41" s="126"/>
-      <c r="E41" s="126"/>
-      <c r="F41" s="104">
+      <c r="D41" s="125"/>
+      <c r="E41" s="125"/>
+      <c r="F41" s="103">
         <f t="shared" si="3"/>
         <v>44500</v>
       </c>
     </row>
     <row r="42" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B42" s="128" t="s">
-        <v>120</v>
-      </c>
-      <c r="C42" s="127">
-        <v>0</v>
-      </c>
-      <c r="D42" s="126"/>
-      <c r="E42" s="126"/>
-      <c r="F42" s="104">
+      <c r="B42" s="127" t="s">
+        <v>119</v>
+      </c>
+      <c r="C42" s="126">
+        <v>0</v>
+      </c>
+      <c r="D42" s="125"/>
+      <c r="E42" s="125"/>
+      <c r="F42" s="103">
         <f t="shared" si="3"/>
         <v>44500</v>
       </c>
     </row>
     <row r="43" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B43" s="128" t="s">
-        <v>119</v>
-      </c>
-      <c r="C43" s="127">
-        <v>0</v>
-      </c>
-      <c r="D43" s="126"/>
-      <c r="E43" s="126"/>
-      <c r="F43" s="104">
+      <c r="B43" s="127" t="s">
+        <v>118</v>
+      </c>
+      <c r="C43" s="126">
+        <v>0</v>
+      </c>
+      <c r="D43" s="125"/>
+      <c r="E43" s="125"/>
+      <c r="F43" s="103">
         <f t="shared" si="3"/>
         <v>44500</v>
       </c>
     </row>
     <row r="44" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B44" s="125" t="s">
-        <v>118</v>
-      </c>
-      <c r="C44" s="124">
-        <v>0</v>
-      </c>
-      <c r="D44" s="123"/>
-      <c r="E44" s="123"/>
-      <c r="F44" s="122">
+      <c r="B44" s="124" t="s">
+        <v>117</v>
+      </c>
+      <c r="C44" s="123">
+        <v>0</v>
+      </c>
+      <c r="D44" s="122"/>
+      <c r="E44" s="122"/>
+      <c r="F44" s="121">
         <f t="shared" si="3"/>
         <v>44500</v>
       </c>
     </row>
     <row r="45" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B45" s="125" t="s">
-        <v>117</v>
-      </c>
-      <c r="C45" s="124">
-        <v>0</v>
-      </c>
-      <c r="D45" s="123"/>
-      <c r="E45" s="123"/>
-      <c r="F45" s="122">
+      <c r="B45" s="124" t="s">
+        <v>116</v>
+      </c>
+      <c r="C45" s="123">
+        <v>0</v>
+      </c>
+      <c r="D45" s="122"/>
+      <c r="E45" s="122"/>
+      <c r="F45" s="121">
         <f>+F43+C45-D45</f>
         <v>44500</v>
       </c>
     </row>
     <row r="46" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B46" s="125" t="s">
-        <v>116</v>
-      </c>
-      <c r="C46" s="124">
-        <v>0</v>
-      </c>
-      <c r="D46" s="123"/>
-      <c r="E46" s="123"/>
-      <c r="F46" s="122">
+      <c r="B46" s="124" t="s">
+        <v>115</v>
+      </c>
+      <c r="C46" s="123">
+        <v>0</v>
+      </c>
+      <c r="D46" s="122"/>
+      <c r="E46" s="122"/>
+      <c r="F46" s="121">
         <f>+F44+C46-D46</f>
         <v>44500</v>
       </c>
     </row>
     <row r="47" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B47" s="121" t="s">
-        <v>115</v>
-      </c>
-      <c r="C47" s="120">
+      <c r="B47" s="120" t="s">
+        <v>114</v>
+      </c>
+      <c r="C47" s="119">
         <f>-A47</f>
         <v>0</v>
       </c>
-      <c r="D47" s="119"/>
-      <c r="E47" s="119"/>
-      <c r="F47" s="118">
+      <c r="D47" s="118"/>
+      <c r="E47" s="118"/>
+      <c r="F47" s="117">
         <f>+F45+C47-D47</f>
         <v>44500</v>
       </c>
